--- a/public/assets/excel/Exemple Gestion de tresorerie.xlsx
+++ b/public/assets/excel/Exemple Gestion de tresorerie.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Stagiaire\Desktop\Laravel\GestionDeTresorerie\public\assets\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rabah\Desktop\Projects\Laravel\Gesteion_tresorerie\public\assets\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A224A343-289B-4EC9-9162-C55200815D38}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CC8BF13-0CB3-4904-BEBB-F0126316E77E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" activeTab="2" xr2:uid="{3F6A7A5B-EA6D-40EF-8400-0D617359E206}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{3F6A7A5B-EA6D-40EF-8400-0D617359E206}"/>
   </bookViews>
   <sheets>
     <sheet name="Prévisions Dépenses-Décaiss" sheetId="2" r:id="rId1"/>
@@ -24,6 +24,20 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -257,10 +271,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="143">
-  <si>
-    <t>Prévisions Dépenses / Charges 2025</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="125">
   <si>
     <t>Elements                     Periodes</t>
   </si>
@@ -487,9 +498,6 @@
     <t>TOTAL</t>
   </si>
   <si>
-    <t>Prévisions Encaissements 2025</t>
-  </si>
-  <si>
     <t>Janvier  8-15</t>
   </si>
   <si>
@@ -583,9 +591,6 @@
     <t>Janvier 24-30-21</t>
   </si>
   <si>
-    <t>FLUX DE TRESORERIE ET GESTION BUDGETAIRE 2025</t>
-  </si>
-  <si>
     <t>Encaissements</t>
   </si>
   <si>
@@ -634,58 +639,13 @@
     <t>Hhenkel</t>
   </si>
   <si>
-    <t>A</t>
+    <t>FLUX DE TRESORERIE ET GESTION BUDGETAIRE</t>
   </si>
   <si>
-    <t>B</t>
+    <t>Prévisions Encaissements</t>
   </si>
   <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>H</t>
-  </si>
-  <si>
-    <t>I</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>R</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>O</t>
-  </si>
-  <si>
-    <t>P</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>Z</t>
-  </si>
-  <si>
-    <t>T</t>
-  </si>
-  <si>
-    <t>U</t>
-  </si>
-  <si>
-    <t>AZ</t>
+    <t>Prévisions Dépenses</t>
   </si>
 </sst>
 </file>
@@ -1216,7 +1176,165 @@
       <font>
         <b/>
         <i val="0"/>
+        <strike val="0"/>
         <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
       </font>
     </dxf>
     <dxf>
@@ -1316,1076 +1434,6 @@
         <i val="0"/>
         <color rgb="FFC00000"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFC00000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFC00000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFC00000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFC00000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFC00000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFC00000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFC00000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFC00000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFC00000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFC00000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFC00000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFC00000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFC00000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFC00000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFC00000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFC00000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFC00000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="4.9989318521683403E-2"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="4.9989318521683403E-2"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="4.9989318521683403E-2"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="4.9989318521683403E-2"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="4.9989318521683403E-2"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="4.9989318521683403E-2"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="4.9989318521683403E-2"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="4.9989318521683403E-2"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="4.9989318521683403E-2"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="4.9989318521683403E-2"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="4.9989318521683403E-2"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="4.9989318521683403E-2"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="4.9989318521683403E-2"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="4.9989318521683403E-2"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="4.9989318521683403E-2"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="4.9989318521683403E-2"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="4.9989318521683403E-2"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="4.9989318521683403E-2"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="4.9989318521683403E-2"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="4.9989318521683403E-2"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="4.9989318521683403E-2"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="4.9989318521683403E-2"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="4.9989318521683403E-2"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="4.9989318521683403E-2"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
@@ -4040,37 +3088,481 @@
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="4.9989318521683403E-2"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
     </dxf>
     <dxf>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="4.9989318521683403E-2"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
     </dxf>
     <dxf>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="4.9989318521683403E-2"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
     </dxf>
     <dxf>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="4.9989318521683403E-2"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
     </dxf>
     <dxf>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="4.9989318521683403E-2"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
     </dxf>
     <dxf>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="4.9989318521683403E-2"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="4.9989318521683403E-2"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="4.9989318521683403E-2"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="4.9989318521683403E-2"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="4.9989318521683403E-2"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="4.9989318521683403E-2"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="4.9989318521683403E-2"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
     </dxf>
     <dxf>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
@@ -4116,37 +3608,505 @@
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="4.9989318521683403E-2"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="4.9989318521683403E-2"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="4.9989318521683403E-2"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="4.9989318521683403E-2"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="4.9989318521683403E-2"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="4.9989318521683403E-2"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="4.9989318521683403E-2"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="4.9989318521683403E-2"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="4.9989318521683403E-2"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="4.9989318521683403E-2"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="4.9989318521683403E-2"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="4.9989318521683403E-2"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
@@ -4222,8 +4182,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="1984375" y="377825"/>
-          <a:ext cx="17313275" cy="2517775"/>
+          <a:off x="1960563" y="396875"/>
+          <a:ext cx="16803687" cy="2651125"/>
           <a:chOff x="0" y="0"/>
           <a:chExt cx="12246" cy="2419"/>
         </a:xfrm>
@@ -9289,8 +9249,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="2650217" y="185057"/>
-          <a:ext cx="17224375" cy="2453368"/>
+          <a:off x="2587624" y="190500"/>
+          <a:ext cx="16788946" cy="2524125"/>
           <a:chOff x="0" y="0"/>
           <a:chExt cx="12246" cy="2419"/>
         </a:xfrm>
@@ -14356,8 +14316,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="1993900" y="127000"/>
-          <a:ext cx="17691100" cy="2133600"/>
+          <a:off x="1968500" y="127000"/>
+          <a:ext cx="17192625" cy="2286000"/>
           <a:chOff x="0" y="0"/>
           <a:chExt cx="12246" cy="2419"/>
         </a:xfrm>
@@ -19402,7 +19362,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Prévisions Dépenses-Décaiss"/>
@@ -20119,41 +20079,41 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AF3D80A9-D626-4953-80E7-7BCDA348B27D}" name="Tableau1" displayName="Tableau1" ref="C25:N37" totalsRowCount="1" dataDxfId="211" totalsRowDxfId="210" totalsRowBorderDxfId="209">
   <autoFilter ref="C25:N36" xr:uid="{75FB0C63-1164-4572-BC32-02D27FC2FD98}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{558D8A28-D7D3-44F7-ADE9-44431091497F}" name="Janvier 1-7" totalsRowFunction="custom" dataDxfId="208" totalsRowDxfId="64">
+    <tableColumn id="1" xr3:uid="{558D8A28-D7D3-44F7-ADE9-44431091497F}" name="Janvier 1-7" totalsRowFunction="custom" dataDxfId="208" totalsRowDxfId="207">
       <calculatedColumnFormula>SUM(C21:C25)</calculatedColumnFormula>
       <totalsRowFormula>SUM(C32:C36)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{D7D3DE1F-1D78-48B9-9406-237AC531A9FB}" name="Janvier 8-15" totalsRowFunction="custom" dataDxfId="207" totalsRowDxfId="63">
+    <tableColumn id="9" xr3:uid="{D7D3DE1F-1D78-48B9-9406-237AC531A9FB}" name="Janvier 8-15" totalsRowFunction="custom" dataDxfId="206" totalsRowDxfId="205">
       <totalsRowFormula>SUM(D32:D36)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{4B1D0F51-6F3B-4966-BFC5-4800FD5DFFDD}" name="Janvier 16-23" totalsRowFunction="custom" dataDxfId="206" totalsRowDxfId="62">
+    <tableColumn id="10" xr3:uid="{4B1D0F51-6F3B-4966-BFC5-4800FD5DFFDD}" name="Janvier 16-23" totalsRowFunction="custom" dataDxfId="204" totalsRowDxfId="203">
       <totalsRowFormula>SUM(E32:E36)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{B91CD431-5124-4EAD-BEE3-51B3E3546349}" name="Janvier 24-31" totalsRowFunction="custom" dataDxfId="205" totalsRowDxfId="61">
+    <tableColumn id="19" xr3:uid="{B91CD431-5124-4EAD-BEE3-51B3E3546349}" name="Janvier 24-31" totalsRowFunction="custom" dataDxfId="202" totalsRowDxfId="201">
       <totalsRowFormula>SUM(F32:F36)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0451F1CD-A493-4C6A-A1D4-2899EF1176B6}" name="Fevrier 1-7" totalsRowFunction="custom" dataDxfId="204" totalsRowDxfId="60">
+    <tableColumn id="2" xr3:uid="{0451F1CD-A493-4C6A-A1D4-2899EF1176B6}" name="Fevrier 1-7" totalsRowFunction="custom" dataDxfId="200" totalsRowDxfId="199">
       <totalsRowFormula>SUM(G32:G36)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{B3E8DFCF-041E-4857-A464-6F487A41ED02}" name="Fevrier 8-15" totalsRowFunction="custom" dataDxfId="203" totalsRowDxfId="59">
+    <tableColumn id="20" xr3:uid="{B3E8DFCF-041E-4857-A464-6F487A41ED02}" name="Fevrier 8-15" totalsRowFunction="custom" dataDxfId="198" totalsRowDxfId="197">
       <totalsRowFormula>SUM(H32:H36)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{53A16F55-D5EA-4711-8180-F117D240CD93}" name="Fevrier 16-23" totalsRowFunction="custom" dataDxfId="202" totalsRowDxfId="58">
+    <tableColumn id="11" xr3:uid="{53A16F55-D5EA-4711-8180-F117D240CD93}" name="Fevrier 16-23" totalsRowFunction="custom" dataDxfId="196" totalsRowDxfId="195">
       <totalsRowFormula>SUM(I32:I36)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{35F7A06E-7400-4F6F-BAAB-18598DACE8B8}" name="Fevrier 24-28" totalsRowFunction="custom" dataDxfId="201" totalsRowDxfId="57">
+    <tableColumn id="21" xr3:uid="{35F7A06E-7400-4F6F-BAAB-18598DACE8B8}" name="Fevrier 24-28" totalsRowFunction="custom" dataDxfId="194" totalsRowDxfId="193">
       <totalsRowFormula>SUM(J32:J36)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{F7BEBE41-986B-4594-B3E3-90E2D726837E}" name="Mars 1-7" totalsRowFunction="custom" dataDxfId="200" totalsRowDxfId="56">
+    <tableColumn id="3" xr3:uid="{F7BEBE41-986B-4594-B3E3-90E2D726837E}" name="Mars 1-7" totalsRowFunction="custom" dataDxfId="192" totalsRowDxfId="191">
       <totalsRowFormula>SUM(K32:K36)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{BC4B3FA5-D98D-439B-BAA8-36CD4C4D6B96}" name="Mars 8-15" totalsRowFunction="custom" dataDxfId="199" totalsRowDxfId="55">
+    <tableColumn id="22" xr3:uid="{BC4B3FA5-D98D-439B-BAA8-36CD4C4D6B96}" name="Mars 8-15" totalsRowFunction="custom" dataDxfId="190" totalsRowDxfId="189">
       <totalsRowFormula>SUM(L32:L36)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{BE964575-BBE9-4E9C-A5AF-4BA6FAF52EA6}" name="Mars 16-23" totalsRowFunction="custom" dataDxfId="198" totalsRowDxfId="54">
+    <tableColumn id="12" xr3:uid="{BE964575-BBE9-4E9C-A5AF-4BA6FAF52EA6}" name="Mars 16-23" totalsRowFunction="custom" dataDxfId="188" totalsRowDxfId="187">
       <totalsRowFormula>SUM(M32:M36)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{21D43377-F22A-45A8-80D6-4B023464C82A}" name="Mars 24-31" totalsRowFunction="custom" dataDxfId="197" totalsRowDxfId="53">
+    <tableColumn id="23" xr3:uid="{21D43377-F22A-45A8-80D6-4B023464C82A}" name="Mars 24-31" totalsRowFunction="custom" dataDxfId="186" totalsRowDxfId="185">
       <totalsRowFormula>SUM(N32:N36)</totalsRowFormula>
     </tableColumn>
   </tableColumns>
@@ -20162,86 +20122,86 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{AF61F0DA-157E-4AD8-857B-EE518080DDA6}" name="Tableau13811" displayName="Tableau13811" ref="C57:N83" totalsRowShown="0" dataDxfId="144" totalsRowDxfId="143" totalsRowBorderDxfId="142">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{AF61F0DA-157E-4AD8-857B-EE518080DDA6}" name="Tableau13811" displayName="Tableau13811" ref="C57:N83" totalsRowShown="0" dataDxfId="120" totalsRowDxfId="119" totalsRowBorderDxfId="118">
   <autoFilter ref="C57:N83" xr:uid="{54156477-891D-4071-8A70-4172E1497415}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{80ECE105-95BD-442D-A33D-2AB509568EE1}" name="Avril 1-7" dataDxfId="141" totalsRowDxfId="140"/>
-    <tableColumn id="9" xr3:uid="{B4BC065A-7698-40AB-8B23-638A42C54FE8}" name="Avril 8-15" dataDxfId="139" totalsRowDxfId="138"/>
-    <tableColumn id="10" xr3:uid="{B858522D-3DEF-4498-A4E2-90DCBC2FDBE1}" name="Avril 16-23" dataDxfId="137" totalsRowDxfId="136"/>
-    <tableColumn id="19" xr3:uid="{376A44D8-F581-412B-84DB-9BE030263B44}" name="Avril 24-30" dataDxfId="135" totalsRowDxfId="134"/>
-    <tableColumn id="2" xr3:uid="{5DD4B458-6ACD-4798-B2AE-724A893148FE}" name="Mai 1-7" dataDxfId="133" totalsRowDxfId="132"/>
-    <tableColumn id="20" xr3:uid="{33C5A14B-2522-47D5-8D30-FC30571F3120}" name="Mai 8-15" dataDxfId="131" totalsRowDxfId="130"/>
-    <tableColumn id="11" xr3:uid="{E22DF93B-463F-440C-AA1D-061FB8CB1788}" name="Mai 16-23" dataDxfId="129" totalsRowDxfId="128"/>
-    <tableColumn id="21" xr3:uid="{65028CCE-9338-4287-A638-325038A8738B}" name="Mai 24-31" dataDxfId="127" totalsRowDxfId="126"/>
-    <tableColumn id="3" xr3:uid="{638DA967-90B5-4640-8296-BF2A82ECA5BD}" name="Juin 1-7" dataDxfId="125" totalsRowDxfId="124"/>
-    <tableColumn id="22" xr3:uid="{980F138B-0A01-4DA1-A3B7-F8A36B77533F}" name="Juin 8-15" dataDxfId="123" totalsRowDxfId="122"/>
-    <tableColumn id="12" xr3:uid="{B83C0964-76F4-42F3-9834-33D3CB6C8347}" name="Juin 16-23" dataDxfId="121" totalsRowDxfId="120"/>
-    <tableColumn id="23" xr3:uid="{2C6D12D1-A9BC-4385-8608-D6AC7C7AA5CD}" name="Juin 24-30" dataDxfId="119" totalsRowDxfId="118"/>
+    <tableColumn id="1" xr3:uid="{80ECE105-95BD-442D-A33D-2AB509568EE1}" name="Avril 1-7" dataDxfId="117" totalsRowDxfId="116"/>
+    <tableColumn id="9" xr3:uid="{B4BC065A-7698-40AB-8B23-638A42C54FE8}" name="Avril 8-15" dataDxfId="115" totalsRowDxfId="114"/>
+    <tableColumn id="10" xr3:uid="{B858522D-3DEF-4498-A4E2-90DCBC2FDBE1}" name="Avril 16-23" dataDxfId="113" totalsRowDxfId="112"/>
+    <tableColumn id="19" xr3:uid="{376A44D8-F581-412B-84DB-9BE030263B44}" name="Avril 24-30" dataDxfId="111" totalsRowDxfId="110"/>
+    <tableColumn id="2" xr3:uid="{5DD4B458-6ACD-4798-B2AE-724A893148FE}" name="Mai 1-7" dataDxfId="109" totalsRowDxfId="108"/>
+    <tableColumn id="20" xr3:uid="{33C5A14B-2522-47D5-8D30-FC30571F3120}" name="Mai 8-15" dataDxfId="107" totalsRowDxfId="106"/>
+    <tableColumn id="11" xr3:uid="{E22DF93B-463F-440C-AA1D-061FB8CB1788}" name="Mai 16-23" dataDxfId="105" totalsRowDxfId="104"/>
+    <tableColumn id="21" xr3:uid="{65028CCE-9338-4287-A638-325038A8738B}" name="Mai 24-31" dataDxfId="103" totalsRowDxfId="102"/>
+    <tableColumn id="3" xr3:uid="{638DA967-90B5-4640-8296-BF2A82ECA5BD}" name="Juin 1-7" dataDxfId="101" totalsRowDxfId="100"/>
+    <tableColumn id="22" xr3:uid="{980F138B-0A01-4DA1-A3B7-F8A36B77533F}" name="Juin 8-15" dataDxfId="99" totalsRowDxfId="98"/>
+    <tableColumn id="12" xr3:uid="{B83C0964-76F4-42F3-9834-33D3CB6C8347}" name="Juin 16-23" dataDxfId="97" totalsRowDxfId="96"/>
+    <tableColumn id="23" xr3:uid="{2C6D12D1-A9BC-4385-8608-D6AC7C7AA5CD}" name="Juin 24-30" dataDxfId="95" totalsRowDxfId="94"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{6532B229-3A6C-4B1C-B9B6-843FD15DDB28}" name="Tableau1381112" displayName="Tableau1381112" ref="C92:J122" totalsRowShown="0" dataDxfId="117" totalsRowDxfId="116" totalsRowBorderDxfId="115">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{6532B229-3A6C-4B1C-B9B6-843FD15DDB28}" name="Tableau1381112" displayName="Tableau1381112" ref="C92:J122" totalsRowShown="0" dataDxfId="93" totalsRowDxfId="92" totalsRowBorderDxfId="91">
   <autoFilter ref="C92:J122" xr:uid="{466C14A4-563F-4C36-97E2-74174DC4EBC6}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{384F9924-9C50-41D7-BF2B-B6A61B22B75E}" name="Juillet 1-7" dataDxfId="114" totalsRowDxfId="113"/>
-    <tableColumn id="9" xr3:uid="{C142E9A9-CBFD-488C-AA92-835E13668097}" name="Juillet 8-15" dataDxfId="112" totalsRowDxfId="111"/>
-    <tableColumn id="10" xr3:uid="{8E30A247-5D91-4C3B-8CE5-E651A2934118}" name="Juillet 16-23" dataDxfId="110" totalsRowDxfId="109"/>
-    <tableColumn id="19" xr3:uid="{9D389E14-AAD8-4DCB-B700-E4F3C9083455}" name="Juillet 24-31" dataDxfId="108" totalsRowDxfId="107"/>
-    <tableColumn id="2" xr3:uid="{2163346F-817C-4EED-A942-B3C02B334E60}" name="Aout 1-7" dataDxfId="106" totalsRowDxfId="105"/>
-    <tableColumn id="20" xr3:uid="{FE90F9CE-EC1F-4D4C-8619-71FD3931AFEB}" name="Aout 8-15" dataDxfId="104" totalsRowDxfId="103"/>
-    <tableColumn id="11" xr3:uid="{2BDBF1BD-FE0A-45A6-8FD9-1696A624877D}" name="Aout 16-23" dataDxfId="102" totalsRowDxfId="101"/>
-    <tableColumn id="21" xr3:uid="{0F960060-8193-40B2-8211-9D9D5222FF7A}" name="Aout 24-31" dataDxfId="100" totalsRowDxfId="99"/>
+    <tableColumn id="1" xr3:uid="{384F9924-9C50-41D7-BF2B-B6A61B22B75E}" name="Juillet 1-7" dataDxfId="90" totalsRowDxfId="89"/>
+    <tableColumn id="9" xr3:uid="{C142E9A9-CBFD-488C-AA92-835E13668097}" name="Juillet 8-15" dataDxfId="88" totalsRowDxfId="87"/>
+    <tableColumn id="10" xr3:uid="{8E30A247-5D91-4C3B-8CE5-E651A2934118}" name="Juillet 16-23" dataDxfId="86" totalsRowDxfId="85"/>
+    <tableColumn id="19" xr3:uid="{9D389E14-AAD8-4DCB-B700-E4F3C9083455}" name="Juillet 24-31" dataDxfId="84" totalsRowDxfId="83"/>
+    <tableColumn id="2" xr3:uid="{2163346F-817C-4EED-A942-B3C02B334E60}" name="Aout 1-7" dataDxfId="82" totalsRowDxfId="81"/>
+    <tableColumn id="20" xr3:uid="{FE90F9CE-EC1F-4D4C-8619-71FD3931AFEB}" name="Aout 8-15" dataDxfId="80" totalsRowDxfId="79"/>
+    <tableColumn id="11" xr3:uid="{2BDBF1BD-FE0A-45A6-8FD9-1696A624877D}" name="Aout 16-23" dataDxfId="78" totalsRowDxfId="77"/>
+    <tableColumn id="21" xr3:uid="{0F960060-8193-40B2-8211-9D9D5222FF7A}" name="Aout 24-31" dataDxfId="76" totalsRowDxfId="75"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{F0B06C6B-3B34-4DA1-A360-20A8CA7D8C98}" name="Tableau14" displayName="Tableau14" ref="K92:N104" totalsRowShown="0" headerRowDxfId="98">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{F0B06C6B-3B34-4DA1-A360-20A8CA7D8C98}" name="Tableau14" displayName="Tableau14" ref="K92:N104" totalsRowShown="0" headerRowDxfId="74">
   <autoFilter ref="K92:N104" xr:uid="{6499C1C1-663B-45B6-9E4E-753C5DF01C7A}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{5E465DD0-6954-497C-978B-D07EFD840073}" name="Septembre 1-7" dataDxfId="97"/>
-    <tableColumn id="2" xr3:uid="{EA2A2252-386B-4735-8BEF-94B3ABB46102}" name="Septembre 8-15" dataDxfId="96"/>
-    <tableColumn id="3" xr3:uid="{8FF2497B-4049-45C2-B23D-0BF2ABD872FB}" name="Septembre 16-23" dataDxfId="95"/>
-    <tableColumn id="4" xr3:uid="{922BBB1D-7BCC-4516-834B-09A5474C3B1F}" name="Septembre 24-30" dataDxfId="94"/>
+    <tableColumn id="1" xr3:uid="{5E465DD0-6954-497C-978B-D07EFD840073}" name="Septembre 1-7" dataDxfId="73"/>
+    <tableColumn id="2" xr3:uid="{EA2A2252-386B-4735-8BEF-94B3ABB46102}" name="Septembre 8-15" dataDxfId="72"/>
+    <tableColumn id="3" xr3:uid="{8FF2497B-4049-45C2-B23D-0BF2ABD872FB}" name="Septembre 16-23" dataDxfId="71"/>
+    <tableColumn id="4" xr3:uid="{922BBB1D-7BCC-4516-834B-09A5474C3B1F}" name="Septembre 24-30" dataDxfId="70"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{DB89E2B8-7FCE-4145-9BED-81FA48476D47}" name="Tableau138111217" displayName="Tableau138111217" ref="C125:J155" totalsRowShown="0" dataDxfId="93" totalsRowDxfId="92" totalsRowBorderDxfId="91">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{DB89E2B8-7FCE-4145-9BED-81FA48476D47}" name="Tableau138111217" displayName="Tableau138111217" ref="C125:J155" totalsRowShown="0" dataDxfId="69" totalsRowDxfId="68" totalsRowBorderDxfId="67">
   <autoFilter ref="C125:J155" xr:uid="{5042F6FA-5DD5-4FEA-86C1-A93F7C9C68C7}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{184A4B8F-0DA9-4456-813D-6C4F5B52EAC9}" name="Octobre 1-7" dataDxfId="90" totalsRowDxfId="89"/>
-    <tableColumn id="9" xr3:uid="{791E8437-2F67-4672-BC26-0467DB6325B5}" name="Octobre 8-15" dataDxfId="88" totalsRowDxfId="87"/>
-    <tableColumn id="10" xr3:uid="{7BD3A439-D5AC-4F47-A4F0-2900678EABFF}" name="Octobre 16-23" dataDxfId="86" totalsRowDxfId="85"/>
-    <tableColumn id="19" xr3:uid="{2DCCF444-DC39-4DED-873E-CB0F8D54092D}" name="Octobre 24-30" dataDxfId="84" totalsRowDxfId="83"/>
-    <tableColumn id="2" xr3:uid="{05B320F3-C7C5-409B-8466-9E64F8D8B68E}" name="Novembre 1-7" dataDxfId="82" totalsRowDxfId="81"/>
-    <tableColumn id="20" xr3:uid="{D95ABD5B-977E-4B20-AC76-D0D7DDBD775C}" name="Novembre 8-15" dataDxfId="80" totalsRowDxfId="79"/>
-    <tableColumn id="11" xr3:uid="{4C22F37E-DFE4-43E2-9698-C1F22156BDA1}" name="Novembre 16-23" dataDxfId="78" totalsRowDxfId="77"/>
-    <tableColumn id="21" xr3:uid="{67CE1607-4D6D-45AF-ACE5-033F27A52EC1}" name="Novembre 24-30" dataDxfId="76" totalsRowDxfId="75"/>
+    <tableColumn id="1" xr3:uid="{184A4B8F-0DA9-4456-813D-6C4F5B52EAC9}" name="Octobre 1-7" dataDxfId="66" totalsRowDxfId="65"/>
+    <tableColumn id="9" xr3:uid="{791E8437-2F67-4672-BC26-0467DB6325B5}" name="Octobre 8-15" dataDxfId="64" totalsRowDxfId="63"/>
+    <tableColumn id="10" xr3:uid="{7BD3A439-D5AC-4F47-A4F0-2900678EABFF}" name="Octobre 16-23" dataDxfId="62" totalsRowDxfId="61"/>
+    <tableColumn id="19" xr3:uid="{2DCCF444-DC39-4DED-873E-CB0F8D54092D}" name="Octobre 24-30" dataDxfId="60" totalsRowDxfId="59"/>
+    <tableColumn id="2" xr3:uid="{05B320F3-C7C5-409B-8466-9E64F8D8B68E}" name="Novembre 1-7" dataDxfId="58" totalsRowDxfId="57"/>
+    <tableColumn id="20" xr3:uid="{D95ABD5B-977E-4B20-AC76-D0D7DDBD775C}" name="Novembre 8-15" dataDxfId="56" totalsRowDxfId="55"/>
+    <tableColumn id="11" xr3:uid="{4C22F37E-DFE4-43E2-9698-C1F22156BDA1}" name="Novembre 16-23" dataDxfId="54" totalsRowDxfId="53"/>
+    <tableColumn id="21" xr3:uid="{67CE1607-4D6D-45AF-ACE5-033F27A52EC1}" name="Novembre 24-30" dataDxfId="52" totalsRowDxfId="51"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{48AEE3A1-FEA9-44AD-BEAE-458CEB17025F}" name="Tableau1418" displayName="Tableau1418" ref="K125:S137" totalsRowShown="0" headerRowDxfId="74">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{48AEE3A1-FEA9-44AD-BEAE-458CEB17025F}" name="Tableau1418" displayName="Tableau1418" ref="K125:S137" totalsRowShown="0" headerRowDxfId="50">
   <autoFilter ref="K125:S137" xr:uid="{1378618F-4F44-4E8F-8360-FE2699FC9790}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{E270B5B4-15B8-4377-80B1-5EE9FCEA4DE6}" name="Decembre 1-7" dataDxfId="73"/>
-    <tableColumn id="2" xr3:uid="{9E7FD2E0-2FD2-4412-9D90-1F5B23A08A86}" name="Decembre 8-15" dataDxfId="72"/>
-    <tableColumn id="3" xr3:uid="{99AE49F3-41ED-4F56-B295-250AF3764368}" name="Decembre 16-23" dataDxfId="71"/>
-    <tableColumn id="4" xr3:uid="{AC950598-8B17-47A6-8820-AB691874C9B6}" name="Decembre 24-30" dataDxfId="70"/>
-    <tableColumn id="6" xr3:uid="{17576730-C9BB-4DE2-9162-A3B8E6352A3A}" name="Janvier 1-7" dataDxfId="69"/>
-    <tableColumn id="9" xr3:uid="{83761B09-1DEA-4265-9946-66AEEF21E55E}" name="Janvier 8-15" dataDxfId="68"/>
-    <tableColumn id="8" xr3:uid="{0DBFFE2A-4400-41E8-B0D2-EEC5EEFF9583}" name="Janvier 16-23" dataDxfId="67"/>
-    <tableColumn id="7" xr3:uid="{5D711004-D7AD-4EB9-85C8-C8C6297EC8F6}" name="Janvier 24-31" dataDxfId="66"/>
-    <tableColumn id="5" xr3:uid="{1F70CC70-E668-47AF-AD10-9BB745FF51C9}" name="TOTAL" dataDxfId="65"/>
+    <tableColumn id="1" xr3:uid="{E270B5B4-15B8-4377-80B1-5EE9FCEA4DE6}" name="Decembre 1-7" dataDxfId="49"/>
+    <tableColumn id="2" xr3:uid="{9E7FD2E0-2FD2-4412-9D90-1F5B23A08A86}" name="Decembre 8-15" dataDxfId="48"/>
+    <tableColumn id="3" xr3:uid="{99AE49F3-41ED-4F56-B295-250AF3764368}" name="Decembre 16-23" dataDxfId="47"/>
+    <tableColumn id="4" xr3:uid="{AC950598-8B17-47A6-8820-AB691874C9B6}" name="Decembre 24-30" dataDxfId="46"/>
+    <tableColumn id="6" xr3:uid="{17576730-C9BB-4DE2-9162-A3B8E6352A3A}" name="Janvier 1-7" dataDxfId="45"/>
+    <tableColumn id="9" xr3:uid="{83761B09-1DEA-4265-9946-66AEEF21E55E}" name="Janvier 8-15" dataDxfId="44"/>
+    <tableColumn id="8" xr3:uid="{0DBFFE2A-4400-41E8-B0D2-EEC5EEFF9583}" name="Janvier 16-23" dataDxfId="43"/>
+    <tableColumn id="7" xr3:uid="{5D711004-D7AD-4EB9-85C8-C8C6297EC8F6}" name="Janvier 24-31" dataDxfId="42"/>
+    <tableColumn id="5" xr3:uid="{1F70CC70-E668-47AF-AD10-9BB745FF51C9}" name="TOTAL" dataDxfId="41"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -20251,7 +20211,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FA5F7B4B-3C82-4869-B349-0ECF367361D2}" name="Tableau3" displayName="Tableau3" ref="C43:N56" totalsRowShown="0">
   <autoFilter ref="C43:N56" xr:uid="{15FB33E1-4EC1-49F9-94DD-B4F9FBF4C0F6}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{A1C0CFC0-B603-4C7E-9306-8F397CEF207B}" name="Avril 1-7" dataDxfId="196">
+    <tableColumn id="1" xr3:uid="{A1C0CFC0-B603-4C7E-9306-8F397CEF207B}" name="Avril 1-7" dataDxfId="184">
       <calculatedColumnFormula>SUM(C39:C43)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{7EFBB66B-2B0E-4668-A94F-6E09D63C36A8}" name="Avril 8-15"/>
@@ -20274,7 +20234,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{F9F8F922-58A5-4844-9707-39D4A1A5840A}" name="Tableau4" displayName="Tableau4" ref="C61:N74" totalsRowShown="0">
   <autoFilter ref="C61:N74" xr:uid="{C8AD9097-4FCC-4A17-BB8C-035E487FEBB5}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{6818B897-680D-4BCA-B1F2-56CBB6D1043F}" name="Juillet 1-7" dataDxfId="195">
+    <tableColumn id="1" xr3:uid="{6818B897-680D-4BCA-B1F2-56CBB6D1043F}" name="Juillet 1-7" dataDxfId="183">
       <calculatedColumnFormula>SUM(C57:C61)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{12747EC6-4FFC-4F83-90A4-05FA91413B7E}" name="Juillet 8-15"/>
@@ -20297,7 +20257,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{5B6A4A3A-3AB0-429F-AC6C-FD322D4DF5D2}" name="Tableau413" displayName="Tableau413" ref="C79:R92" totalsRowShown="0">
   <autoFilter ref="C79:R92" xr:uid="{C62B9082-01AD-4611-82B4-8545BD52DB7F}"/>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{950981C0-7E9F-4635-B15F-552CDAD87F3F}" name="Octobre 1-7" dataDxfId="194">
+    <tableColumn id="1" xr3:uid="{950981C0-7E9F-4635-B15F-552CDAD87F3F}" name="Octobre 1-7" dataDxfId="182">
       <calculatedColumnFormula>SUM(C75:C79)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{293F3024-0A33-4FCB-8AA6-7D0DAD9127BB}" name="Octobre 8-15"/>
@@ -20314,7 +20274,7 @@
     <tableColumn id="14" xr3:uid="{E1FA8F2D-71B0-4CC7-8179-C3581DBD898E}" name="janvier 8-15-21"/>
     <tableColumn id="15" xr3:uid="{BBAA41B3-89A0-432B-B2E9-E43C73E5DFD4}" name="janvier 16-23-21"/>
     <tableColumn id="16" xr3:uid="{7B11B1D8-7393-4409-A5F0-90AF68CE37ED}" name="janvier 24-31-21"/>
-    <tableColumn id="17" xr3:uid="{838F004E-9629-4297-B242-6D1025A7A1F8}" name="TOTAL" dataDxfId="193">
+    <tableColumn id="17" xr3:uid="{838F004E-9629-4297-B242-6D1025A7A1F8}" name="TOTAL" dataDxfId="181">
       <calculatedColumnFormula>SUM(C26:N26,C44:N44,C62:N62,Tableau413[[#This Row],[Octobre 1-7]:[janvier 24-31-21]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -20323,43 +20283,43 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{9FDD1885-A23B-40F6-B2BF-D20E46C79E83}" name="Tableau13" displayName="Tableau13" ref="C24:N36" totalsRowCount="1" dataDxfId="192" totalsRowDxfId="191" totalsRowBorderDxfId="190">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{9FDD1885-A23B-40F6-B2BF-D20E46C79E83}" name="Tableau13" displayName="Tableau13" ref="C24:N36" totalsRowCount="1" dataDxfId="180" totalsRowDxfId="179" totalsRowBorderDxfId="178">
   <autoFilter ref="C24:N35" xr:uid="{75FB0C63-1164-4572-BC32-02D27FC2FD98}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{44096E9E-ABCE-42F5-B038-AB7D3F42E2A8}" name="Janvier 1-7" totalsRowFunction="custom" dataDxfId="189" totalsRowDxfId="52">
+    <tableColumn id="1" xr3:uid="{44096E9E-ABCE-42F5-B038-AB7D3F42E2A8}" name="Janvier 1-7" totalsRowFunction="custom" dataDxfId="177" totalsRowDxfId="176">
       <totalsRowFormula>SUM(Tableau13[Janvier 1-7])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{38686C36-55D4-4254-8ACC-8F0B90E8B522}" name="Janvier  8-15" totalsRowFunction="custom" dataDxfId="188" totalsRowDxfId="51">
+    <tableColumn id="9" xr3:uid="{38686C36-55D4-4254-8ACC-8F0B90E8B522}" name="Janvier  8-15" totalsRowFunction="custom" dataDxfId="175" totalsRowDxfId="174">
       <totalsRowFormula>SUM(Tableau13[Janvier  8-15])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{37A42A80-0B6C-41BA-B72D-D7EED36AF74E}" name="Janvier  16-23" totalsRowFunction="custom" dataDxfId="187" totalsRowDxfId="50">
+    <tableColumn id="10" xr3:uid="{37A42A80-0B6C-41BA-B72D-D7EED36AF74E}" name="Janvier  16-23" totalsRowFunction="custom" dataDxfId="173" totalsRowDxfId="172">
       <totalsRowFormula>SUM(Tableau13[Janvier  16-23])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{D5B9D2AF-6E30-412D-99D2-253DC7C4A598}" name="Janvier  24-31" totalsRowFunction="custom" dataDxfId="186" totalsRowDxfId="49">
+    <tableColumn id="19" xr3:uid="{D5B9D2AF-6E30-412D-99D2-253DC7C4A598}" name="Janvier  24-31" totalsRowFunction="custom" dataDxfId="171" totalsRowDxfId="170">
       <totalsRowFormula>SUM(Tableau13[Janvier  24-31])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{6982DF49-D7B2-49F0-84A9-3C139C05DCF2}" name="Fevrier 1-7" totalsRowFunction="custom" dataDxfId="185" totalsRowDxfId="48">
+    <tableColumn id="2" xr3:uid="{6982DF49-D7B2-49F0-84A9-3C139C05DCF2}" name="Fevrier 1-7" totalsRowFunction="custom" dataDxfId="169" totalsRowDxfId="168">
       <totalsRowFormula>SUM(Tableau13[Fevrier 1-7])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{4142FE91-BE8E-480B-9EEC-A22C7279B668}" name="Fevrier 8-15" totalsRowFunction="custom" dataDxfId="184" totalsRowDxfId="47">
+    <tableColumn id="20" xr3:uid="{4142FE91-BE8E-480B-9EEC-A22C7279B668}" name="Fevrier 8-15" totalsRowFunction="custom" dataDxfId="167" totalsRowDxfId="166">
       <totalsRowFormula>SUM(Tableau13[Fevrier 8-15])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{233AB0E9-07BF-44B9-9059-9339F708E683}" name="Fevrier 16-23" totalsRowFunction="custom" dataDxfId="183" totalsRowDxfId="46">
+    <tableColumn id="11" xr3:uid="{233AB0E9-07BF-44B9-9059-9339F708E683}" name="Fevrier 16-23" totalsRowFunction="custom" dataDxfId="165" totalsRowDxfId="164">
       <totalsRowFormula>SUM(Tableau13[Fevrier 16-23])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{2C4343EE-522A-4648-B4A4-3C11B5CAB2DC}" name="Fevrier 24-28" totalsRowFunction="custom" dataDxfId="182" totalsRowDxfId="45">
+    <tableColumn id="21" xr3:uid="{2C4343EE-522A-4648-B4A4-3C11B5CAB2DC}" name="Fevrier 24-28" totalsRowFunction="custom" dataDxfId="163" totalsRowDxfId="162">
       <totalsRowFormula>SUM(Tableau13[Fevrier 24-28])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{88D382A8-58D5-4E35-932C-05B39E9D0C78}" name="Mars 1-7" totalsRowFunction="custom" dataDxfId="181" totalsRowDxfId="44">
+    <tableColumn id="3" xr3:uid="{88D382A8-58D5-4E35-932C-05B39E9D0C78}" name="Mars 1-7" totalsRowFunction="custom" dataDxfId="161" totalsRowDxfId="160">
       <totalsRowFormula>SUM(Tableau13[Mars 1-7])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{6244C7AE-C50E-40A0-A6D1-839C771C873C}" name="Mars 8-15" totalsRowFunction="custom" dataDxfId="180" totalsRowDxfId="43">
+    <tableColumn id="22" xr3:uid="{6244C7AE-C50E-40A0-A6D1-839C771C873C}" name="Mars 8-15" totalsRowFunction="custom" dataDxfId="159" totalsRowDxfId="158">
       <totalsRowFormula>SUM(Tableau13[Mars 8-15])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{A9A2CB48-F3EC-4B90-B107-82B9D8EDAC88}" name="Mars 16-23" totalsRowFunction="custom" dataDxfId="179" totalsRowDxfId="42">
+    <tableColumn id="12" xr3:uid="{A9A2CB48-F3EC-4B90-B107-82B9D8EDAC88}" name="Mars 16-23" totalsRowFunction="custom" dataDxfId="157" totalsRowDxfId="156">
       <totalsRowFormula>SUM(Tableau13[Mars 16-23])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{126768E5-8CD7-4FA1-971C-FBC5F840E74D}" name="Mars 24-31" totalsRowFunction="custom" dataDxfId="178" totalsRowDxfId="41">
+    <tableColumn id="23" xr3:uid="{126768E5-8CD7-4FA1-971C-FBC5F840E74D}" name="Mars 24-31" totalsRowFunction="custom" dataDxfId="155" totalsRowDxfId="154">
       <totalsRowFormula>SUM(Tableau13[Mars 24-31])</totalsRowFormula>
     </tableColumn>
   </tableColumns>
@@ -20371,7 +20331,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{066C5582-251F-4F32-9F3F-E2D08FC3809D}" name="Tableau36" displayName="Tableau36" ref="C41:N53" totalsRowShown="0">
   <autoFilter ref="C41:N53" xr:uid="{15FB33E1-4EC1-49F9-94DD-B4F9FBF4C0F6}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{4F7FD835-7B65-4EC0-B254-7093527786DB}" name="Avril 1-7" dataDxfId="177">
+    <tableColumn id="1" xr3:uid="{4F7FD835-7B65-4EC0-B254-7093527786DB}" name="Avril 1-7" dataDxfId="153">
       <calculatedColumnFormula>SUM(C31:C41)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{078829C2-B978-43EB-9338-D80737C0DC26}" name="Avril 8-15"/>
@@ -20394,7 +20354,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{CEE2144E-F5FB-432D-83E3-EB5D0BBF9A0A}" name="Tableau47" displayName="Tableau47" ref="C58:N70" totalsRowShown="0">
   <autoFilter ref="C58:N70" xr:uid="{C8AD9097-4FCC-4A17-BB8C-035E487FEBB5}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{2DF478B4-6C6C-4770-8C7A-6B9C0604EE9B}" name="Juillet 1-7" dataDxfId="176">
+    <tableColumn id="1" xr3:uid="{2DF478B4-6C6C-4770-8C7A-6B9C0604EE9B}" name="Juillet 1-7" dataDxfId="152">
       <calculatedColumnFormula>SUM(C48:C58)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{EF0D9A3B-BB4C-4F35-84DE-9F482A4C2B80}" name="Juillet 8-15"/>
@@ -20404,7 +20364,7 @@
     <tableColumn id="6" xr3:uid="{096E60B5-D258-4B35-A5D1-FD6A3E690977}" name="Aout 8-15"/>
     <tableColumn id="7" xr3:uid="{C1D47205-6499-46D8-8045-6070416EED58}" name="Aout 16-23"/>
     <tableColumn id="8" xr3:uid="{35763DB7-5882-4E7E-B997-BDFD9A573260}" name="Aout 24-31"/>
-    <tableColumn id="9" xr3:uid="{E59824EE-4FEC-4C2A-A51F-AD66F7CF7518}" name="Septembre 1-7" dataDxfId="175"/>
+    <tableColumn id="9" xr3:uid="{E59824EE-4FEC-4C2A-A51F-AD66F7CF7518}" name="Septembre 1-7" dataDxfId="151"/>
     <tableColumn id="10" xr3:uid="{D33CBCE8-3DE2-4FDF-A0DC-2770E8D20DFC}" name="Septembre 8-15"/>
     <tableColumn id="11" xr3:uid="{8EF74A2E-8BA1-4567-81F5-6BD4D3A520B0}" name="Septembre 16-23"/>
     <tableColumn id="12" xr3:uid="{B17C9EAC-C4C2-4BF1-82B8-6D4134BFE989}" name="Septembre 24-30"/>
@@ -20417,7 +20377,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{DA32DB00-AA49-4EB1-821C-20822BE69B52}" name="Tableau4714" displayName="Tableau4714" ref="C75:S87" totalsRowShown="0">
   <autoFilter ref="C75:S87" xr:uid="{2B9B3B4F-08AD-4145-B331-E37D74D791A7}"/>
   <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{19780783-603C-480F-9C62-0121AC0816A9}" name="Octobre 1-7" dataDxfId="174">
+    <tableColumn id="1" xr3:uid="{19780783-603C-480F-9C62-0121AC0816A9}" name="Octobre 1-7" dataDxfId="150">
       <calculatedColumnFormula>SUM(C65:C75)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{36A3B920-FFBA-4566-A097-0BFD46E0FAD3}" name="Octobre 8-15"/>
@@ -20427,7 +20387,7 @@
     <tableColumn id="6" xr3:uid="{87D672F2-D2B9-4801-A8DD-D7F7556A8828}" name="Novembre 8-15"/>
     <tableColumn id="7" xr3:uid="{FDDCEE86-EECF-463B-9947-E2B08C2FD1CE}" name="Novembre 16-23"/>
     <tableColumn id="8" xr3:uid="{5446033F-CF0C-448F-8A87-3C6D857D1FCD}" name="Novembre 24-30"/>
-    <tableColumn id="9" xr3:uid="{B0DC1E5A-E178-4C28-9A38-BEB90D5E9E5C}" name="Decembre 1-7" dataDxfId="173"/>
+    <tableColumn id="9" xr3:uid="{B0DC1E5A-E178-4C28-9A38-BEB90D5E9E5C}" name="Decembre 1-7" dataDxfId="149"/>
     <tableColumn id="10" xr3:uid="{F5161E10-55AD-41F8-AA48-009D0FC2019C}" name="Decembre 8-15"/>
     <tableColumn id="11" xr3:uid="{DBAF2CED-D420-46E8-9241-281A81080378}" name="Decembre 16-23"/>
     <tableColumn id="12" xr3:uid="{50E24C50-8B25-4B0E-AEA1-3C710D438036}" name="Decembre 24-30"/>
@@ -20435,7 +20395,7 @@
     <tableColumn id="14" xr3:uid="{BFBB3CAC-C294-4FEF-BFD9-2A572B22BBB0}" name="Janvier 8-15-21"/>
     <tableColumn id="15" xr3:uid="{CCC2EDD6-1CFA-434D-B1E8-E62CEF6D35C9}" name="Janvier 16-23-21"/>
     <tableColumn id="16" xr3:uid="{4FB80EC0-783D-4C41-81D4-A1C2EF85CF58}" name="Janvier 24-30-21"/>
-    <tableColumn id="17" xr3:uid="{12A2D508-A376-4368-B28E-E10CB449635E}" name="TOTAL" dataDxfId="172">
+    <tableColumn id="17" xr3:uid="{12A2D508-A376-4368-B28E-E10CB449635E}" name="TOTAL" dataDxfId="148">
       <calculatedColumnFormula>SUM(S65:S75)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -20444,30 +20404,30 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{5E8E52EF-8C73-4CCF-868B-9F86731A378B}" name="Tableau138" displayName="Tableau138" ref="C22:N48" totalsRowShown="0" dataDxfId="171" totalsRowDxfId="170" totalsRowBorderDxfId="169">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{5E8E52EF-8C73-4CCF-868B-9F86731A378B}" name="Tableau138" displayName="Tableau138" ref="C22:N48" totalsRowShown="0" dataDxfId="147" totalsRowDxfId="146" totalsRowBorderDxfId="145">
   <autoFilter ref="C22:N48" xr:uid="{75FB0C63-1164-4572-BC32-02D27FC2FD98}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{77A62CFF-4D37-43C7-9A4B-541C5978ECB2}" name="Janvier 1-7" dataDxfId="168" totalsRowDxfId="167"/>
-    <tableColumn id="9" xr3:uid="{778FC184-0AF2-485B-8297-E71524294DE6}" name="Janvier 8-15" dataDxfId="166" totalsRowDxfId="165"/>
-    <tableColumn id="10" xr3:uid="{393804FE-C0B6-46A2-AEE2-AA6782DD5F15}" name="Janvier 16-23" dataDxfId="164" totalsRowDxfId="163"/>
-    <tableColumn id="19" xr3:uid="{AEEA916F-25A0-4EAB-BFCF-5616883C5F6C}" name="Janvier 24-31" dataDxfId="162" totalsRowDxfId="161"/>
-    <tableColumn id="2" xr3:uid="{800EB8CB-589C-4B5C-AD22-EFC8B9C3BBFF}" name="Fevrier 1-7" dataDxfId="160" totalsRowDxfId="159"/>
-    <tableColumn id="20" xr3:uid="{028D49A0-85A6-4C41-9847-04727B3344AC}" name="Fevrier 8-15" dataDxfId="158" totalsRowDxfId="157"/>
-    <tableColumn id="11" xr3:uid="{FCB876AC-4E7A-4A20-AA11-A38C59A016DA}" name="Fevrier 16-23" dataDxfId="156" totalsRowDxfId="155"/>
-    <tableColumn id="21" xr3:uid="{2B24BF23-C1FE-4E2D-A97E-997B50B9E9F2}" name="Fevrier 24-28" dataDxfId="154" totalsRowDxfId="153"/>
-    <tableColumn id="3" xr3:uid="{350F1505-0DD5-4ADB-A9F5-A813D451AE1A}" name="Mars 1-7" dataDxfId="152" totalsRowDxfId="151"/>
-    <tableColumn id="22" xr3:uid="{D93DC0FA-4D1A-49E7-A4EC-20E63B61D8D3}" name="Mars 8-15" dataDxfId="150" totalsRowDxfId="149"/>
-    <tableColumn id="12" xr3:uid="{8DB04595-F1FB-4091-A494-56D05A870866}" name="Mars 16-23" dataDxfId="148" totalsRowDxfId="147"/>
-    <tableColumn id="23" xr3:uid="{D00C2E46-F817-4CA9-8AB7-9AE05B373B42}" name="Mars 24-31" dataDxfId="146" totalsRowDxfId="145"/>
+    <tableColumn id="1" xr3:uid="{77A62CFF-4D37-43C7-9A4B-541C5978ECB2}" name="Janvier 1-7" dataDxfId="144" totalsRowDxfId="143"/>
+    <tableColumn id="9" xr3:uid="{778FC184-0AF2-485B-8297-E71524294DE6}" name="Janvier 8-15" dataDxfId="142" totalsRowDxfId="141"/>
+    <tableColumn id="10" xr3:uid="{393804FE-C0B6-46A2-AEE2-AA6782DD5F15}" name="Janvier 16-23" dataDxfId="140" totalsRowDxfId="139"/>
+    <tableColumn id="19" xr3:uid="{AEEA916F-25A0-4EAB-BFCF-5616883C5F6C}" name="Janvier 24-31" dataDxfId="138" totalsRowDxfId="137"/>
+    <tableColumn id="2" xr3:uid="{800EB8CB-589C-4B5C-AD22-EFC8B9C3BBFF}" name="Fevrier 1-7" dataDxfId="136" totalsRowDxfId="135"/>
+    <tableColumn id="20" xr3:uid="{028D49A0-85A6-4C41-9847-04727B3344AC}" name="Fevrier 8-15" dataDxfId="134" totalsRowDxfId="133"/>
+    <tableColumn id="11" xr3:uid="{FCB876AC-4E7A-4A20-AA11-A38C59A016DA}" name="Fevrier 16-23" dataDxfId="132" totalsRowDxfId="131"/>
+    <tableColumn id="21" xr3:uid="{2B24BF23-C1FE-4E2D-A97E-997B50B9E9F2}" name="Fevrier 24-28" dataDxfId="130" totalsRowDxfId="129"/>
+    <tableColumn id="3" xr3:uid="{350F1505-0DD5-4ADB-A9F5-A813D451AE1A}" name="Mars 1-7" dataDxfId="128" totalsRowDxfId="127"/>
+    <tableColumn id="22" xr3:uid="{D93DC0FA-4D1A-49E7-A4EC-20E63B61D8D3}" name="Mars 8-15" dataDxfId="126" totalsRowDxfId="125"/>
+    <tableColumn id="12" xr3:uid="{8DB04595-F1FB-4091-A494-56D05A870866}" name="Mars 16-23" dataDxfId="124" totalsRowDxfId="123"/>
+    <tableColumn id="23" xr3:uid="{D00C2E46-F817-4CA9-8AB7-9AE05B373B42}" name="Mars 24-31" dataDxfId="122" totalsRowDxfId="121"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -20505,7 +20465,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -20611,7 +20571,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -20753,7 +20713,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -20762,33 +20722,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEF4CD38-5443-44CC-8C0D-44D2703700F4}">
   <dimension ref="A19:X93"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" customWidth="1"/>
-    <col min="2" max="2" width="21.109375" customWidth="1"/>
-    <col min="3" max="3" width="20.44140625" customWidth="1"/>
-    <col min="4" max="4" width="22.21875" customWidth="1"/>
-    <col min="5" max="5" width="27.109375" customWidth="1"/>
-    <col min="6" max="6" width="32.109375" customWidth="1"/>
-    <col min="7" max="7" width="22.6640625" customWidth="1"/>
-    <col min="8" max="8" width="18.44140625" customWidth="1"/>
-    <col min="9" max="9" width="19.6640625" customWidth="1"/>
-    <col min="10" max="10" width="20.21875" customWidth="1"/>
-    <col min="11" max="11" width="20.109375" customWidth="1"/>
-    <col min="12" max="12" width="19.109375" customWidth="1"/>
-    <col min="13" max="13" width="24.88671875" customWidth="1"/>
-    <col min="14" max="14" width="22.21875" customWidth="1"/>
-    <col min="15" max="15" width="24.6640625" customWidth="1"/>
-    <col min="16" max="17" width="21.44140625" customWidth="1"/>
+    <col min="1" max="1" width="12.5703125" customWidth="1"/>
+    <col min="2" max="2" width="21.140625" customWidth="1"/>
+    <col min="3" max="3" width="20.42578125" customWidth="1"/>
+    <col min="4" max="4" width="22.28515625" customWidth="1"/>
+    <col min="5" max="5" width="27.140625" customWidth="1"/>
+    <col min="6" max="6" width="32.140625" customWidth="1"/>
+    <col min="7" max="7" width="22.7109375" customWidth="1"/>
+    <col min="8" max="8" width="18.42578125" customWidth="1"/>
+    <col min="9" max="9" width="19.7109375" customWidth="1"/>
+    <col min="10" max="10" width="20.28515625" customWidth="1"/>
+    <col min="11" max="11" width="20.140625" customWidth="1"/>
+    <col min="12" max="12" width="19.140625" customWidth="1"/>
+    <col min="13" max="13" width="24.85546875" customWidth="1"/>
+    <col min="14" max="14" width="22.28515625" customWidth="1"/>
+    <col min="15" max="15" width="24.7109375" customWidth="1"/>
+    <col min="16" max="17" width="21.42578125" customWidth="1"/>
     <col min="18" max="18" width="26" customWidth="1"/>
-    <col min="19" max="19" width="13.88671875" customWidth="1"/>
-    <col min="20" max="23" width="13.44140625" customWidth="1"/>
+    <col min="19" max="19" width="13.85546875" customWidth="1"/>
+    <col min="20" max="23" width="13.42578125" customWidth="1"/>
     <col min="24" max="24" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="C19" s="54" t="s">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="D19" s="54"/>
       <c r="E19" s="54"/>
@@ -20801,7 +20761,7 @@
       <c r="L19" s="54"/>
       <c r="M19" s="54"/>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="C20" s="54"/>
       <c r="D20" s="54"/>
       <c r="E20" s="54"/>
@@ -20814,7 +20774,7 @@
       <c r="L20" s="54"/>
       <c r="M20" s="54"/>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="C21" s="54"/>
       <c r="D21" s="54"/>
       <c r="E21" s="54"/>
@@ -20827,54 +20787,54 @@
       <c r="L21" s="54"/>
       <c r="M21" s="54"/>
     </row>
-    <row r="25" spans="1:14" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="43" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B25" s="44"/>
       <c r="C25" t="s">
+        <v>1</v>
+      </c>
+      <c r="D25" t="s">
         <v>2</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>3</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>4</v>
       </c>
-      <c r="F25" t="s">
+      <c r="G25" t="s">
         <v>5</v>
       </c>
-      <c r="G25" t="s">
+      <c r="H25" t="s">
         <v>6</v>
       </c>
-      <c r="H25" t="s">
+      <c r="I25" t="s">
         <v>7</v>
       </c>
-      <c r="I25" t="s">
+      <c r="J25" t="s">
         <v>8</v>
       </c>
-      <c r="J25" t="s">
+      <c r="K25" t="s">
         <v>9</v>
       </c>
-      <c r="K25" t="s">
+      <c r="L25" t="s">
         <v>10</v>
       </c>
-      <c r="L25" t="s">
+      <c r="M25" t="s">
         <v>11</v>
       </c>
-      <c r="M25" t="s">
+      <c r="N25" t="s">
         <v>12</v>
       </c>
-      <c r="N25" t="s">
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" s="45" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="45" t="s">
+      <c r="B26" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
@@ -20889,10 +20849,10 @@
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="46"/>
       <c r="B27" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
@@ -20907,10 +20867,10 @@
       <c r="M27" s="2"/>
       <c r="N27" s="2"/>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="46"/>
       <c r="B28" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
@@ -20925,10 +20885,10 @@
       <c r="M28" s="2"/>
       <c r="N28" s="2"/>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="46"/>
       <c r="B29" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
@@ -20943,10 +20903,10 @@
       <c r="M29" s="2"/>
       <c r="N29" s="2"/>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="47"/>
       <c r="B30" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
@@ -20961,9 +20921,9 @@
       <c r="M30" s="2"/>
       <c r="N30" s="2"/>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="48" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B31" s="48"/>
       <c r="C31" s="3">
@@ -21015,12 +20975,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="45" t="s">
+        <v>20</v>
+      </c>
+      <c r="B32" s="4" t="s">
         <v>21</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>22</v>
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
@@ -21035,10 +20995,10 @@
       <c r="M32" s="5"/>
       <c r="N32" s="5"/>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A33" s="46"/>
       <c r="B33" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C33" s="6"/>
       <c r="D33" s="6"/>
@@ -21053,10 +21013,10 @@
       <c r="M33" s="6"/>
       <c r="N33" s="6"/>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A34" s="46"/>
       <c r="B34" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
@@ -21071,10 +21031,10 @@
       <c r="M34" s="2"/>
       <c r="N34" s="2"/>
     </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A35" s="46"/>
       <c r="B35" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
@@ -21089,10 +21049,10 @@
       <c r="M35" s="2"/>
       <c r="N35" s="2"/>
     </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A36" s="47"/>
       <c r="B36" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
@@ -21107,9 +21067,9 @@
       <c r="M36" s="2"/>
       <c r="N36" s="2"/>
     </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A37" s="48" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B37" s="48"/>
       <c r="C37" s="8">
@@ -21161,9 +21121,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A38" s="49" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B38" s="49"/>
       <c r="C38" s="9">
@@ -21215,9 +21175,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A39" s="50" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B39" s="50"/>
       <c r="C39" s="51">
@@ -21242,106 +21202,106 @@
       <c r="M39" s="52"/>
       <c r="N39" s="53"/>
       <c r="X39" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>30</v>
       </c>
+      <c r="C40" t="s">
+        <v>31</v>
+      </c>
+      <c r="D40" t="s">
+        <v>31</v>
+      </c>
+      <c r="E40" t="s">
+        <v>31</v>
+      </c>
+      <c r="F40" t="s">
+        <v>31</v>
+      </c>
+      <c r="G40" t="s">
+        <v>31</v>
+      </c>
+      <c r="H40" t="s">
+        <v>31</v>
+      </c>
+      <c r="I40" t="s">
+        <v>31</v>
+      </c>
+      <c r="J40" t="s">
+        <v>31</v>
+      </c>
+      <c r="K40" t="s">
+        <v>31</v>
+      </c>
+      <c r="L40" t="s">
+        <v>31</v>
+      </c>
+      <c r="P40" t="s">
+        <v>31</v>
+      </c>
+      <c r="X40" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>31</v>
-      </c>
-      <c r="C40" t="s">
-        <v>32</v>
-      </c>
-      <c r="D40" t="s">
-        <v>32</v>
-      </c>
-      <c r="E40" t="s">
-        <v>32</v>
-      </c>
-      <c r="F40" t="s">
-        <v>32</v>
-      </c>
-      <c r="G40" t="s">
-        <v>32</v>
-      </c>
-      <c r="H40" t="s">
-        <v>32</v>
-      </c>
-      <c r="I40" t="s">
-        <v>32</v>
-      </c>
-      <c r="J40" t="s">
-        <v>32</v>
-      </c>
-      <c r="K40" t="s">
-        <v>32</v>
-      </c>
-      <c r="L40" t="s">
-        <v>32</v>
-      </c>
-      <c r="P40" t="s">
-        <v>32</v>
-      </c>
-      <c r="X40" t="s">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="B41" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="B41" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="43" spans="1:24" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:24" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="43" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B43" s="44"/>
       <c r="C43" t="s">
+        <v>34</v>
+      </c>
+      <c r="D43" t="s">
         <v>35</v>
       </c>
-      <c r="D43" t="s">
+      <c r="E43" t="s">
         <v>36</v>
       </c>
-      <c r="E43" t="s">
+      <c r="F43" t="s">
         <v>37</v>
       </c>
-      <c r="F43" t="s">
+      <c r="G43" t="s">
         <v>38</v>
       </c>
-      <c r="G43" t="s">
+      <c r="H43" t="s">
         <v>39</v>
       </c>
-      <c r="H43" t="s">
+      <c r="I43" t="s">
         <v>40</v>
       </c>
-      <c r="I43" t="s">
+      <c r="J43" t="s">
         <v>41</v>
       </c>
-      <c r="J43" t="s">
+      <c r="K43" t="s">
         <v>42</v>
       </c>
-      <c r="K43" t="s">
+      <c r="L43" t="s">
         <v>43</v>
       </c>
-      <c r="L43" t="s">
+      <c r="M43" t="s">
         <v>44</v>
       </c>
-      <c r="M43" t="s">
+      <c r="N43" t="s">
         <v>45</v>
       </c>
-      <c r="N43" t="s">
+      <c r="R43" t="s">
         <v>46</v>
       </c>
-      <c r="R43" t="s">
-        <v>47</v>
-      </c>
     </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A44" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="C44" s="2"/>
       <c r="F44" s="2"/>
@@ -21352,10 +21312,10 @@
       <c r="K44" s="2"/>
       <c r="N44" s="2"/>
     </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A45" s="46"/>
       <c r="B45" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C45" s="2"/>
       <c r="E45" s="2"/>
@@ -21365,13 +21325,13 @@
       <c r="M45" s="2"/>
       <c r="N45" s="2"/>
       <c r="P45" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A46" s="46"/>
       <c r="B46" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C46" s="2"/>
       <c r="F46" s="2"/>
@@ -21379,10 +21339,10 @@
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
     </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A47" s="46"/>
       <c r="B47" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
@@ -21394,16 +21354,16 @@
       <c r="L47" s="2"/>
       <c r="M47" s="2"/>
     </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A48" s="47"/>
       <c r="B48" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C48" s="2"/>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="48" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B49" s="48"/>
       <c r="C49" s="3">
@@ -21455,12 +21415,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="45" t="s">
+        <v>20</v>
+      </c>
+      <c r="B50" s="4" t="s">
         <v>21</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>22</v>
       </c>
       <c r="C50" s="5"/>
       <c r="D50" s="5"/>
@@ -21475,10 +21435,10 @@
       <c r="M50" s="5"/>
       <c r="N50" s="5"/>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="46"/>
       <c r="B51" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C51" s="6"/>
       <c r="D51" s="6"/>
@@ -21493,28 +21453,28 @@
       <c r="M51" s="6"/>
       <c r="N51" s="6"/>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="46"/>
       <c r="B52" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C52" s="2"/>
       <c r="N52" s="10"/>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="46"/>
       <c r="B53" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C53" s="2"/>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
       <c r="J53" s="2"/>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="47"/>
       <c r="B54" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
@@ -21527,9 +21487,9 @@
       <c r="M54" s="2"/>
       <c r="N54" s="2"/>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="48" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B55" s="48"/>
       <c r="C55" s="3">
@@ -21581,9 +21541,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="49" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B56" s="49"/>
       <c r="C56" s="9">
@@ -21635,9 +21595,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="50" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B57" s="50"/>
       <c r="C57" s="51">
@@ -21662,57 +21622,57 @@
       <c r="M57" s="52"/>
       <c r="N57" s="53"/>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="M58" s="2"/>
     </row>
-    <row r="61" spans="1:14" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:14" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="43" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B61" s="44"/>
       <c r="C61" t="s">
+        <v>47</v>
+      </c>
+      <c r="D61" t="s">
         <v>48</v>
       </c>
-      <c r="D61" t="s">
+      <c r="E61" t="s">
         <v>49</v>
       </c>
-      <c r="E61" t="s">
+      <c r="F61" t="s">
         <v>50</v>
       </c>
-      <c r="F61" t="s">
+      <c r="G61" t="s">
         <v>51</v>
       </c>
-      <c r="G61" t="s">
+      <c r="H61" t="s">
         <v>52</v>
       </c>
-      <c r="H61" t="s">
+      <c r="I61" t="s">
         <v>53</v>
       </c>
-      <c r="I61" t="s">
+      <c r="J61" t="s">
         <v>54</v>
       </c>
-      <c r="J61" t="s">
+      <c r="K61" t="s">
         <v>55</v>
       </c>
-      <c r="K61" t="s">
+      <c r="L61" t="s">
         <v>56</v>
       </c>
-      <c r="L61" t="s">
+      <c r="M61" t="s">
         <v>57</v>
       </c>
-      <c r="M61" t="s">
+      <c r="N61" t="s">
         <v>58</v>
       </c>
-      <c r="N61" t="s">
-        <v>59</v>
-      </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" s="2"/>
@@ -21722,19 +21682,19 @@
       <c r="I62" s="2"/>
       <c r="L62" s="2"/>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="46"/>
       <c r="B63" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C63" s="2"/>
       <c r="G63" s="2"/>
       <c r="I63" s="2"/>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="46"/>
       <c r="B64" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C64" s="2"/>
       <c r="F64" s="2"/>
@@ -21743,10 +21703,10 @@
       <c r="J64" s="2"/>
       <c r="L64" s="2"/>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A65" s="46"/>
       <c r="B65" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" s="2"/>
@@ -21754,16 +21714,16 @@
       <c r="H65" s="2"/>
       <c r="I65" s="2"/>
     </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A66" s="47"/>
       <c r="B66" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C66" s="2"/>
     </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67" s="48" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B67" s="48"/>
       <c r="C67" s="3">
@@ -21815,12 +21775,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68" s="45" t="s">
+        <v>20</v>
+      </c>
+      <c r="B68" s="4" t="s">
         <v>21</v>
-      </c>
-      <c r="B68" s="4" t="s">
-        <v>22</v>
       </c>
       <c r="C68" s="5"/>
       <c r="D68" s="5"/>
@@ -21832,10 +21792,10 @@
       <c r="J68" s="5"/>
       <c r="L68" s="2"/>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A69" s="46"/>
       <c r="B69" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C69" s="6"/>
       <c r="D69" s="6"/>
@@ -21847,33 +21807,33 @@
       <c r="J69" s="6"/>
       <c r="L69" s="2"/>
     </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70" s="46"/>
       <c r="B70" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C70" s="2"/>
     </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A71" s="46"/>
       <c r="B71" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C71" s="2"/>
       <c r="L71" s="2"/>
     </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A72" s="47"/>
       <c r="B72" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C72" s="2"/>
       <c r="F72" s="2"/>
       <c r="H72" s="2"/>
     </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73" s="48" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B73" s="48"/>
       <c r="C73" s="3">
@@ -21925,9 +21885,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74" s="49" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B74" s="49"/>
       <c r="C74" s="9">
@@ -21979,9 +21939,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75" s="50" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B75" s="50"/>
       <c r="C75" s="42">
@@ -22006,79 +21966,79 @@
       <c r="M75" s="42"/>
       <c r="N75" s="42"/>
     </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="K76" s="2"/>
     </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="F77" s="2"/>
       <c r="G77" s="2"/>
       <c r="K77" s="2"/>
     </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="K78" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
-    <row r="79" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="43" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B79" s="44"/>
       <c r="C79" t="s">
+        <v>59</v>
+      </c>
+      <c r="D79" t="s">
         <v>60</v>
       </c>
-      <c r="D79" t="s">
+      <c r="E79" t="s">
         <v>61</v>
       </c>
-      <c r="E79" t="s">
+      <c r="F79" t="s">
         <v>62</v>
       </c>
-      <c r="F79" t="s">
+      <c r="G79" t="s">
         <v>63</v>
       </c>
-      <c r="G79" t="s">
+      <c r="H79" t="s">
         <v>64</v>
       </c>
-      <c r="H79" t="s">
+      <c r="I79" t="s">
         <v>65</v>
       </c>
-      <c r="I79" t="s">
+      <c r="J79" t="s">
         <v>66</v>
       </c>
-      <c r="J79" t="s">
+      <c r="K79" t="s">
         <v>67</v>
       </c>
-      <c r="K79" t="s">
+      <c r="L79" t="s">
         <v>68</v>
       </c>
-      <c r="L79" t="s">
+      <c r="M79" t="s">
         <v>69</v>
       </c>
-      <c r="M79" t="s">
+      <c r="N79" t="s">
         <v>70</v>
       </c>
-      <c r="N79" t="s">
+      <c r="O79" t="s">
         <v>71</v>
       </c>
-      <c r="O79" t="s">
+      <c r="P79" t="s">
         <v>72</v>
       </c>
-      <c r="P79" t="s">
+      <c r="Q79" t="s">
         <v>73</v>
       </c>
-      <c r="Q79" t="s">
+      <c r="R79" t="s">
         <v>74</v>
       </c>
-      <c r="R79" t="s">
-        <v>75</v>
-      </c>
     </row>
-    <row r="80" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="B80" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" s="2"/>
@@ -22090,10 +22050,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="46"/>
       <c r="B81" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C81" s="2"/>
       <c r="F81" s="2"/>
@@ -22103,10 +22063,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="46"/>
       <c r="B82" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C82" s="2"/>
       <c r="F82" s="2"/>
@@ -22117,10 +22077,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="46"/>
       <c r="B83" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" s="2"/>
@@ -22132,10 +22092,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" s="47"/>
       <c r="B84" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C84" s="2"/>
       <c r="R84" s="2">
@@ -22143,9 +22103,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="48" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B85" s="48"/>
       <c r="C85" s="3"/>
@@ -22168,12 +22128,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" s="45" t="s">
+        <v>20</v>
+      </c>
+      <c r="B86" s="4" t="s">
         <v>21</v>
-      </c>
-      <c r="B86" s="4" t="s">
-        <v>22</v>
       </c>
       <c r="C86" s="5"/>
       <c r="D86" s="5"/>
@@ -22189,10 +22149,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" s="46"/>
       <c r="B87" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C87" s="6"/>
       <c r="D87" s="6"/>
@@ -22209,10 +22169,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" s="46"/>
       <c r="B88" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C88" s="2"/>
       <c r="R88" s="2">
@@ -22220,10 +22180,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="46"/>
       <c r="B89" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C89" s="2"/>
       <c r="L89" s="2"/>
@@ -22232,10 +22192,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="47"/>
       <c r="B90" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C90" s="2"/>
       <c r="F90" s="2"/>
@@ -22245,9 +22205,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91" s="48" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B91" s="48"/>
       <c r="C91" s="3">
@@ -22315,9 +22275,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" s="49" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B92" s="49"/>
       <c r="C92" s="9">
@@ -22385,9 +22345,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93" s="50" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B93" s="50"/>
       <c r="C93" s="42">
@@ -22479,37 +22439,37 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B440EB6-42D1-4476-9A36-8102F4A35AF3}">
   <dimension ref="A17:Y123"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="24.44140625" customWidth="1"/>
-    <col min="3" max="3" width="20.44140625" customWidth="1"/>
-    <col min="4" max="4" width="29.21875" customWidth="1"/>
-    <col min="5" max="5" width="29.44140625" customWidth="1"/>
-    <col min="6" max="6" width="25.44140625" customWidth="1"/>
+    <col min="2" max="2" width="24.42578125" customWidth="1"/>
+    <col min="3" max="3" width="20.42578125" customWidth="1"/>
+    <col min="4" max="4" width="29.28515625" customWidth="1"/>
+    <col min="5" max="5" width="29.42578125" customWidth="1"/>
+    <col min="6" max="6" width="25.42578125" customWidth="1"/>
     <col min="7" max="7" width="23" customWidth="1"/>
-    <col min="8" max="8" width="19.88671875" customWidth="1"/>
-    <col min="9" max="9" width="20.88671875" customWidth="1"/>
-    <col min="10" max="10" width="20.6640625" customWidth="1"/>
-    <col min="11" max="11" width="20.109375" customWidth="1"/>
-    <col min="12" max="12" width="24.109375" customWidth="1"/>
-    <col min="13" max="13" width="24.88671875" customWidth="1"/>
+    <col min="8" max="8" width="19.85546875" customWidth="1"/>
+    <col min="9" max="9" width="20.85546875" customWidth="1"/>
+    <col min="10" max="10" width="20.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.140625" customWidth="1"/>
+    <col min="12" max="12" width="24.140625" customWidth="1"/>
+    <col min="13" max="13" width="24.85546875" customWidth="1"/>
     <col min="14" max="14" width="23" customWidth="1"/>
     <col min="15" max="15" width="29" customWidth="1"/>
-    <col min="16" max="16" width="23.44140625" customWidth="1"/>
-    <col min="17" max="17" width="18.109375" customWidth="1"/>
-    <col min="18" max="18" width="18.88671875" customWidth="1"/>
-    <col min="19" max="19" width="21.21875" customWidth="1"/>
-    <col min="20" max="20" width="32.6640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="20.109375" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.44140625" customWidth="1"/>
+    <col min="16" max="16" width="23.42578125" customWidth="1"/>
+    <col min="17" max="17" width="18.140625" customWidth="1"/>
+    <col min="18" max="18" width="18.85546875" customWidth="1"/>
+    <col min="19" max="19" width="21.28515625" customWidth="1"/>
+    <col min="20" max="20" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.42578125" customWidth="1"/>
     <col min="25" max="25" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="C17" s="54" t="s">
-        <v>76</v>
+        <v>123</v>
       </c>
       <c r="D17" s="54"/>
       <c r="E17" s="54"/>
@@ -22522,7 +22482,7 @@
       <c r="L17" s="54"/>
       <c r="M17" s="54"/>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="C18" s="54"/>
       <c r="D18" s="54"/>
       <c r="E18" s="54"/>
@@ -22535,7 +22495,7 @@
       <c r="L18" s="54"/>
       <c r="M18" s="54"/>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="C19" s="54"/>
       <c r="D19" s="54"/>
       <c r="E19" s="54"/>
@@ -22548,54 +22508,54 @@
       <c r="L19" s="54"/>
       <c r="M19" s="54"/>
     </row>
-    <row r="24" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="43" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B24" s="44"/>
       <c r="C24" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D24" t="s">
+        <v>75</v>
+      </c>
+      <c r="E24" t="s">
+        <v>76</v>
+      </c>
+      <c r="F24" t="s">
         <v>77</v>
       </c>
-      <c r="E24" t="s">
+      <c r="G24" t="s">
+        <v>5</v>
+      </c>
+      <c r="H24" t="s">
+        <v>6</v>
+      </c>
+      <c r="I24" t="s">
+        <v>7</v>
+      </c>
+      <c r="J24" t="s">
+        <v>8</v>
+      </c>
+      <c r="K24" t="s">
+        <v>9</v>
+      </c>
+      <c r="L24" t="s">
+        <v>10</v>
+      </c>
+      <c r="M24" t="s">
+        <v>11</v>
+      </c>
+      <c r="N24" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25" s="58" t="s">
         <v>78</v>
       </c>
-      <c r="F24" t="s">
+      <c r="B25" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="G24" t="s">
-        <v>6</v>
-      </c>
-      <c r="H24" t="s">
-        <v>7</v>
-      </c>
-      <c r="I24" t="s">
-        <v>8</v>
-      </c>
-      <c r="J24" t="s">
-        <v>9</v>
-      </c>
-      <c r="K24" t="s">
-        <v>10</v>
-      </c>
-      <c r="L24" t="s">
-        <v>11</v>
-      </c>
-      <c r="M24" t="s">
-        <v>12</v>
-      </c>
-      <c r="N24" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="58" t="s">
-        <v>80</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>125</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
@@ -22610,10 +22570,10 @@
       <c r="M25" s="2"/>
       <c r="N25" s="2"/>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="59"/>
       <c r="B26" s="1" t="s">
-        <v>126</v>
+        <v>80</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
@@ -22628,10 +22588,10 @@
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="59"/>
       <c r="B27" s="1" t="s">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
@@ -22646,10 +22606,10 @@
       <c r="M27" s="2"/>
       <c r="N27" s="2"/>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="59"/>
       <c r="B28" s="1" t="s">
-        <v>127</v>
+        <v>82</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
@@ -22664,10 +22624,10 @@
       <c r="M28" s="2"/>
       <c r="N28" s="2"/>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="59"/>
       <c r="B29" s="1" t="s">
-        <v>128</v>
+        <v>83</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
@@ -22682,10 +22642,10 @@
       <c r="M29" s="2"/>
       <c r="N29" s="2"/>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="59"/>
       <c r="B30" s="7" t="s">
-        <v>140</v>
+        <v>84</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
@@ -22700,10 +22660,10 @@
       <c r="M30" s="2"/>
       <c r="N30" s="2"/>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="59"/>
       <c r="B31" s="7" t="s">
-        <v>133</v>
+        <v>85</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
@@ -22718,10 +22678,10 @@
       <c r="M31" s="2"/>
       <c r="N31" s="2"/>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="59"/>
       <c r="B32" s="7" t="s">
-        <v>132</v>
+        <v>86</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
@@ -22736,10 +22696,10 @@
       <c r="M32" s="2"/>
       <c r="N32" s="2"/>
     </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A33" s="59"/>
       <c r="B33" s="7" t="s">
-        <v>130</v>
+        <v>87</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
@@ -22754,10 +22714,10 @@
       <c r="M33" s="2"/>
       <c r="N33" s="2"/>
     </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A34" s="59"/>
       <c r="B34" s="7" t="s">
-        <v>135</v>
+        <v>96</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
@@ -22772,9 +22732,9 @@
       <c r="M34" s="2"/>
       <c r="N34" s="2"/>
     </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A35" s="56" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B35" s="57"/>
       <c r="C35" s="2"/>
@@ -22790,9 +22750,9 @@
       <c r="M35" s="2"/>
       <c r="N35" s="2"/>
     </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A36" s="49" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B36" s="49"/>
       <c r="C36" s="12">
@@ -22845,9 +22805,9 @@
       </c>
       <c r="P36" s="13"/>
     </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A37" s="50" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B37" s="50"/>
       <c r="C37" s="51">
@@ -22872,93 +22832,93 @@
       <c r="M37" s="52"/>
       <c r="N37" s="53"/>
       <c r="Y37" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>31</v>
-      </c>
       <c r="B38" s="14" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C38" s="14"/>
       <c r="D38" s="14"/>
       <c r="E38" s="14"/>
       <c r="G38" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="K38" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q38" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y38" t="s">
         <v>32</v>
       </c>
-      <c r="Y38" t="s">
-        <v>33</v>
-      </c>
     </row>
-    <row r="41" spans="1:25" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:25" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="43" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B41" s="44"/>
       <c r="C41" t="s">
+        <v>34</v>
+      </c>
+      <c r="D41" t="s">
         <v>35</v>
       </c>
-      <c r="D41" t="s">
+      <c r="E41" t="s">
         <v>36</v>
       </c>
-      <c r="E41" t="s">
+      <c r="F41" t="s">
         <v>37</v>
       </c>
-      <c r="F41" t="s">
+      <c r="G41" t="s">
         <v>38</v>
       </c>
-      <c r="G41" t="s">
-        <v>39</v>
-      </c>
       <c r="H41" t="s">
+        <v>93</v>
+      </c>
+      <c r="I41" t="s">
+        <v>94</v>
+      </c>
+      <c r="J41" t="s">
         <v>95</v>
       </c>
-      <c r="I41" t="s">
-        <v>96</v>
-      </c>
-      <c r="J41" t="s">
-        <v>97</v>
-      </c>
       <c r="K41" t="s">
+        <v>42</v>
+      </c>
+      <c r="L41" t="s">
         <v>43</v>
       </c>
-      <c r="L41" t="s">
+      <c r="M41" t="s">
         <v>44</v>
       </c>
-      <c r="M41" t="s">
+      <c r="N41" t="s">
         <v>45</v>
       </c>
-      <c r="N41" t="s">
+      <c r="S41" t="s">
         <v>46</v>
       </c>
-      <c r="S41" t="s">
-        <v>47</v>
-      </c>
     </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A42" s="58" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>125</v>
+        <v>79</v>
       </c>
       <c r="C42" s="2"/>
       <c r="E42" s="2"/>
       <c r="G42" s="2"/>
       <c r="K42" s="2"/>
     </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A43" s="59"/>
       <c r="B43" s="1" t="s">
-        <v>139</v>
+        <v>80</v>
       </c>
       <c r="C43" s="2"/>
       <c r="E43" s="2"/>
@@ -22968,33 +22928,33 @@
       <c r="L43" s="2"/>
       <c r="M43" s="2"/>
       <c r="Q43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A44" s="59"/>
       <c r="B44" s="1" t="s">
-        <v>129</v>
+        <v>81</v>
       </c>
       <c r="C44" s="2"/>
       <c r="F44" s="2"/>
       <c r="J44" s="2"/>
       <c r="N44" s="2"/>
     </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A45" s="59"/>
       <c r="B45" s="1" t="s">
-        <v>133</v>
+        <v>82</v>
       </c>
       <c r="C45" s="2"/>
       <c r="E45" s="2"/>
       <c r="G45" s="2"/>
       <c r="K45" s="2"/>
     </row>
-    <row r="46" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A46" s="59"/>
       <c r="B46" s="1" t="s">
-        <v>140</v>
+        <v>83</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" s="15"/>
@@ -23002,19 +22962,19 @@
       <c r="K46" s="2"/>
       <c r="L46" s="2"/>
     </row>
-    <row r="47" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A47" s="59"/>
       <c r="B47" s="7" t="s">
-        <v>138</v>
+        <v>84</v>
       </c>
       <c r="C47" s="2"/>
       <c r="G47" s="2"/>
       <c r="K47" s="2"/>
     </row>
-    <row r="48" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A48" s="59"/>
       <c r="B48" s="7" t="s">
-        <v>141</v>
+        <v>85</v>
       </c>
       <c r="C48" s="2"/>
       <c r="F48" s="2"/>
@@ -23023,46 +22983,46 @@
       <c r="K48" s="2"/>
       <c r="M48" s="2"/>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="59"/>
       <c r="B49" s="7" t="s">
-        <v>131</v>
+        <v>86</v>
       </c>
       <c r="C49" s="2"/>
       <c r="G49" s="2"/>
       <c r="K49" s="2"/>
       <c r="M49" s="2"/>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="59"/>
       <c r="B50" s="7" t="s">
-        <v>136</v>
+        <v>87</v>
       </c>
       <c r="C50" s="2"/>
       <c r="G50" s="2"/>
       <c r="K50" s="2"/>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="59"/>
       <c r="B51" s="7" t="s">
-        <v>137</v>
+        <v>96</v>
       </c>
       <c r="C51" s="2"/>
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
       <c r="K51" s="2"/>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="56" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B52" s="57"/>
       <c r="C52" s="2"/>
       <c r="F52" s="2"/>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="49" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B53" s="49"/>
       <c r="C53" s="9">
@@ -23114,9 +23074,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="50" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B54" s="50"/>
       <c r="C54" s="51">
@@ -23141,63 +23101,63 @@
       <c r="M54" s="52"/>
       <c r="N54" s="53"/>
     </row>
-    <row r="58" spans="1:14" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:14" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="43" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B58" s="44"/>
       <c r="C58" t="s">
+        <v>47</v>
+      </c>
+      <c r="D58" t="s">
         <v>48</v>
       </c>
-      <c r="D58" t="s">
+      <c r="E58" t="s">
         <v>49</v>
       </c>
-      <c r="E58" t="s">
+      <c r="F58" t="s">
         <v>50</v>
       </c>
-      <c r="F58" t="s">
+      <c r="G58" t="s">
         <v>51</v>
       </c>
-      <c r="G58" t="s">
+      <c r="H58" t="s">
         <v>52</v>
       </c>
-      <c r="H58" t="s">
+      <c r="I58" t="s">
         <v>53</v>
       </c>
-      <c r="I58" t="s">
+      <c r="J58" t="s">
         <v>54</v>
       </c>
-      <c r="J58" t="s">
+      <c r="K58" t="s">
         <v>55</v>
       </c>
-      <c r="K58" t="s">
+      <c r="L58" t="s">
         <v>56</v>
       </c>
-      <c r="L58" t="s">
+      <c r="M58" t="s">
         <v>57</v>
       </c>
-      <c r="M58" t="s">
-        <v>58</v>
-      </c>
       <c r="N58" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" s="58" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>142</v>
+        <v>79</v>
       </c>
       <c r="C59" s="2"/>
       <c r="G59" s="2"/>
       <c r="K59" s="2"/>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" s="59"/>
       <c r="B60" s="1" t="s">
-        <v>129</v>
+        <v>80</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" s="2"/>
@@ -23206,28 +23166,28 @@
       <c r="I60" s="2"/>
       <c r="K60" s="2"/>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" s="59"/>
       <c r="B61" s="1" t="s">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="C61" s="2"/>
       <c r="F61" s="2"/>
       <c r="J61" s="2"/>
       <c r="K61" s="2"/>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="59"/>
       <c r="B62" s="1" t="s">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="C62" s="2"/>
       <c r="K62" s="2"/>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="59"/>
       <c r="B63" s="1" t="s">
-        <v>138</v>
+        <v>83</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" s="2"/>
@@ -23237,60 +23197,60 @@
       <c r="J63" s="2"/>
       <c r="K63" s="2"/>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="59"/>
       <c r="B64" s="7" t="s">
-        <v>141</v>
+        <v>84</v>
       </c>
       <c r="C64" s="2"/>
       <c r="K64" s="2"/>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A65" s="59"/>
       <c r="B65" s="7" t="s">
-        <v>131</v>
+        <v>85</v>
       </c>
       <c r="C65" s="2"/>
       <c r="K65" s="2"/>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A66" s="59"/>
       <c r="B66" s="7" t="s">
-        <v>136</v>
+        <v>86</v>
       </c>
       <c r="C66" s="2"/>
       <c r="I66" s="16"/>
       <c r="J66" s="16"/>
       <c r="K66" s="2"/>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A67" s="59"/>
       <c r="B67" s="7" t="s">
-        <v>137</v>
+        <v>87</v>
       </c>
       <c r="C67" s="2"/>
       <c r="K67" s="2"/>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A68" s="59"/>
       <c r="B68" s="7" t="s">
-        <v>134</v>
+        <v>96</v>
       </c>
       <c r="C68" s="2"/>
       <c r="K68" s="2"/>
       <c r="N68" s="15"/>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A69" s="56" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B69" s="57"/>
       <c r="C69" s="2"/>
       <c r="K69" s="2"/>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A70" s="49" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B70" s="49"/>
       <c r="C70" s="9">
@@ -23342,9 +23302,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A71" s="50" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B71" s="50"/>
       <c r="C71" s="42">
@@ -23369,69 +23329,69 @@
       <c r="M71" s="42"/>
       <c r="N71" s="42"/>
     </row>
-    <row r="75" spans="1:19" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:19" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="43" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B75" s="44"/>
       <c r="C75" t="s">
+        <v>59</v>
+      </c>
+      <c r="D75" t="s">
         <v>60</v>
       </c>
-      <c r="D75" t="s">
+      <c r="E75" t="s">
         <v>61</v>
       </c>
-      <c r="E75" t="s">
-        <v>62</v>
-      </c>
       <c r="F75" t="s">
+        <v>99</v>
+      </c>
+      <c r="G75" t="s">
+        <v>63</v>
+      </c>
+      <c r="H75" t="s">
+        <v>64</v>
+      </c>
+      <c r="I75" t="s">
+        <v>65</v>
+      </c>
+      <c r="J75" t="s">
+        <v>100</v>
+      </c>
+      <c r="K75" t="s">
+        <v>67</v>
+      </c>
+      <c r="L75" t="s">
+        <v>68</v>
+      </c>
+      <c r="M75" t="s">
+        <v>69</v>
+      </c>
+      <c r="N75" t="s">
         <v>101</v>
       </c>
-      <c r="G75" t="s">
-        <v>64</v>
-      </c>
-      <c r="H75" t="s">
-        <v>65</v>
-      </c>
-      <c r="I75" t="s">
-        <v>66</v>
-      </c>
-      <c r="J75" t="s">
+      <c r="O75" t="s">
         <v>102</v>
       </c>
-      <c r="K75" t="s">
-        <v>68</v>
-      </c>
-      <c r="L75" t="s">
-        <v>69</v>
-      </c>
-      <c r="M75" t="s">
-        <v>70</v>
-      </c>
-      <c r="N75" t="s">
+      <c r="P75" t="s">
         <v>103</v>
       </c>
-      <c r="O75" t="s">
+      <c r="Q75" t="s">
         <v>104</v>
       </c>
-      <c r="P75" t="s">
+      <c r="R75" t="s">
         <v>105</v>
       </c>
-      <c r="Q75" t="s">
-        <v>106</v>
-      </c>
-      <c r="R75" t="s">
-        <v>107</v>
-      </c>
       <c r="S75" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
-    <row r="76" spans="1:19" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:19" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="58" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>125</v>
+        <v>79</v>
       </c>
       <c r="C76" s="2"/>
       <c r="G76" s="2"/>
@@ -23441,10 +23401,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:19" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:19" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="59"/>
       <c r="B77" s="1" t="s">
-        <v>139</v>
+        <v>80</v>
       </c>
       <c r="C77" s="2"/>
       <c r="E77" s="2"/>
@@ -23456,10 +23416,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:19" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="59"/>
       <c r="B78" s="1" t="s">
-        <v>129</v>
+        <v>81</v>
       </c>
       <c r="C78" s="2"/>
       <c r="F78" s="2"/>
@@ -23470,10 +23430,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:19" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:19" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="59"/>
       <c r="B79" s="1" t="s">
-        <v>133</v>
+        <v>82</v>
       </c>
       <c r="C79" s="2"/>
       <c r="K79" s="2"/>
@@ -23482,10 +23442,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:19" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:19" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="59"/>
       <c r="B80" s="1" t="s">
-        <v>140</v>
+        <v>83</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" s="17"/>
@@ -23501,10 +23461,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:19" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:19" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="59"/>
       <c r="B81" s="7" t="s">
-        <v>138</v>
+        <v>84</v>
       </c>
       <c r="C81" s="2"/>
       <c r="H81" s="2"/>
@@ -23516,10 +23476,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="59"/>
       <c r="B82" s="7" t="s">
-        <v>141</v>
+        <v>85</v>
       </c>
       <c r="C82" s="2"/>
       <c r="H82" s="2"/>
@@ -23531,10 +23491,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="59"/>
       <c r="B83" s="7" t="s">
-        <v>131</v>
+        <v>86</v>
       </c>
       <c r="C83" s="2"/>
       <c r="H83" s="2"/>
@@ -23546,10 +23506,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A84" s="59"/>
       <c r="B84" s="7" t="s">
-        <v>136</v>
+        <v>87</v>
       </c>
       <c r="C84" s="2"/>
       <c r="E84" s="2"/>
@@ -23563,10 +23523,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A85" s="59"/>
       <c r="B85" s="7" t="s">
-        <v>137</v>
+        <v>96</v>
       </c>
       <c r="C85" s="2"/>
       <c r="K85" s="2"/>
@@ -23575,9 +23535,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="56" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B86" s="57"/>
       <c r="C86" s="2"/>
@@ -23587,9 +23547,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="49" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B87" s="49"/>
       <c r="C87" s="9">
@@ -23661,9 +23621,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:19" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:19" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="50" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B88" s="50"/>
       <c r="C88" s="42">
@@ -23699,54 +23659,54 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:19" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="90" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:19" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I90" s="55"/>
       <c r="J90" s="55"/>
     </row>
-    <row r="91" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G91" s="2"/>
       <c r="I91" s="55"/>
       <c r="J91" s="55"/>
     </row>
-    <row r="92" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:19" x14ac:dyDescent="0.25">
       <c r="F92" s="2"/>
       <c r="I92" s="55"/>
       <c r="J92" s="55"/>
       <c r="L92" s="2"/>
     </row>
-    <row r="97" ht="27.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="98" ht="27.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="99" ht="27.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="100" ht="27.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="101" ht="24.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="102" ht="24.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="103" ht="39.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="104" ht="39.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="105" ht="39.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="106" ht="39.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="107" ht="39.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="108" ht="39.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="109" ht="39.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="110" ht="39.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="111" ht="39.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="112" ht="39.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="113" spans="3:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="114" spans="3:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="115" spans="3:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="116" spans="3:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="117" spans="3:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="121" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="97" ht="27.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="27.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="27.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="27.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="39.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="39.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="39.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="39.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="39.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="39.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="39.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="39.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="39.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="39.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" spans="3:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" spans="3:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" spans="3:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" spans="3:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" spans="3:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C121" s="20"/>
       <c r="D121" s="20"/>
       <c r="E121" s="41"/>
       <c r="F121" s="19"/>
     </row>
-    <row r="122" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="122" spans="3:6" x14ac:dyDescent="0.25">
       <c r="E122" s="20"/>
       <c r="F122" s="19"/>
     </row>
-    <row r="123" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="123" spans="3:6" x14ac:dyDescent="0.25">
       <c r="E123" s="20"/>
       <c r="F123" s="19"/>
     </row>
@@ -23808,106 +23768,106 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:AC162"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.5546875" customWidth="1"/>
-    <col min="2" max="2" width="20.109375" customWidth="1"/>
-    <col min="3" max="3" width="25.109375" customWidth="1"/>
-    <col min="4" max="4" width="25.44140625" customWidth="1"/>
+    <col min="1" max="1" width="10.5703125" customWidth="1"/>
+    <col min="2" max="2" width="20.140625" customWidth="1"/>
+    <col min="3" max="3" width="25.140625" customWidth="1"/>
+    <col min="4" max="4" width="25.42578125" customWidth="1"/>
     <col min="5" max="5" width="25" customWidth="1"/>
-    <col min="6" max="6" width="25.44140625" customWidth="1"/>
+    <col min="6" max="6" width="25.42578125" customWidth="1"/>
     <col min="7" max="7" width="23" customWidth="1"/>
-    <col min="8" max="8" width="19.88671875" customWidth="1"/>
-    <col min="9" max="9" width="20.88671875" customWidth="1"/>
-    <col min="10" max="10" width="20.6640625" customWidth="1"/>
-    <col min="11" max="11" width="20.109375" customWidth="1"/>
-    <col min="12" max="12" width="24.109375" customWidth="1"/>
-    <col min="13" max="13" width="24.88671875" customWidth="1"/>
+    <col min="8" max="8" width="19.85546875" customWidth="1"/>
+    <col min="9" max="9" width="20.85546875" customWidth="1"/>
+    <col min="10" max="10" width="20.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.140625" customWidth="1"/>
+    <col min="12" max="12" width="24.140625" customWidth="1"/>
+    <col min="13" max="13" width="24.85546875" customWidth="1"/>
     <col min="14" max="18" width="23" customWidth="1"/>
     <col min="19" max="19" width="29" customWidth="1"/>
-    <col min="20" max="20" width="23.44140625" customWidth="1"/>
-    <col min="21" max="21" width="18.109375" customWidth="1"/>
-    <col min="22" max="22" width="17.44140625" customWidth="1"/>
-    <col min="23" max="24" width="13.88671875" customWidth="1"/>
-    <col min="25" max="28" width="13.44140625" customWidth="1"/>
+    <col min="20" max="20" width="23.42578125" customWidth="1"/>
+    <col min="21" max="21" width="18.140625" customWidth="1"/>
+    <col min="22" max="22" width="17.42578125" customWidth="1"/>
+    <col min="23" max="24" width="13.85546875" customWidth="1"/>
+    <col min="25" max="28" width="13.42578125" customWidth="1"/>
     <col min="29" max="29" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="4:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="4:18" x14ac:dyDescent="0.25">
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
       <c r="R2" s="2"/>
     </row>
-    <row r="3" spans="4:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="4:18" x14ac:dyDescent="0.25">
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
       <c r="R3" s="2"/>
     </row>
-    <row r="4" spans="4:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="4:18" x14ac:dyDescent="0.25">
       <c r="O4" s="2"/>
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
       <c r="R4" s="2"/>
     </row>
-    <row r="5" spans="4:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="4:18" x14ac:dyDescent="0.25">
       <c r="O5" s="2"/>
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
       <c r="R5" s="2"/>
     </row>
-    <row r="6" spans="4:18" x14ac:dyDescent="0.3">
+    <row r="6" spans="4:18" x14ac:dyDescent="0.25">
       <c r="O6" s="2"/>
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
       <c r="R6" s="2"/>
     </row>
-    <row r="7" spans="4:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="4:18" x14ac:dyDescent="0.25">
       <c r="O7" s="2"/>
       <c r="P7" s="2"/>
       <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
     </row>
-    <row r="8" spans="4:18" x14ac:dyDescent="0.3">
+    <row r="8" spans="4:18" x14ac:dyDescent="0.25">
       <c r="O8" s="2"/>
       <c r="P8" s="2"/>
       <c r="Q8" s="2"/>
       <c r="R8" s="2"/>
     </row>
-    <row r="9" spans="4:18" x14ac:dyDescent="0.3">
+    <row r="9" spans="4:18" x14ac:dyDescent="0.25">
       <c r="O9" s="2"/>
       <c r="P9" s="2"/>
       <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
     </row>
-    <row r="10" spans="4:18" x14ac:dyDescent="0.3">
+    <row r="10" spans="4:18" x14ac:dyDescent="0.25">
       <c r="O10" s="2"/>
       <c r="P10" s="2"/>
       <c r="Q10" s="2"/>
       <c r="R10" s="2"/>
     </row>
-    <row r="11" spans="4:18" x14ac:dyDescent="0.3">
+    <row r="11" spans="4:18" x14ac:dyDescent="0.25">
       <c r="O11" s="2"/>
       <c r="P11" s="2"/>
       <c r="Q11" s="2"/>
       <c r="R11" s="2"/>
     </row>
-    <row r="12" spans="4:18" x14ac:dyDescent="0.3">
+    <row r="12" spans="4:18" x14ac:dyDescent="0.25">
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
       <c r="Q12" s="2"/>
       <c r="R12" s="2"/>
     </row>
-    <row r="13" spans="4:18" x14ac:dyDescent="0.3">
+    <row r="13" spans="4:18" x14ac:dyDescent="0.25">
       <c r="O13" s="2"/>
       <c r="P13" s="2"/>
       <c r="Q13" s="2"/>
       <c r="R13" s="2"/>
     </row>
-    <row r="14" spans="4:18" x14ac:dyDescent="0.3">
+    <row r="14" spans="4:18" x14ac:dyDescent="0.25">
       <c r="D14" s="77" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="E14" s="77"/>
       <c r="F14" s="77"/>
@@ -23922,7 +23882,7 @@
       <c r="Q14" s="2"/>
       <c r="R14" s="2"/>
     </row>
-    <row r="15" spans="4:18" x14ac:dyDescent="0.3">
+    <row r="15" spans="4:18" x14ac:dyDescent="0.25">
       <c r="D15" s="77"/>
       <c r="E15" s="77"/>
       <c r="F15" s="77"/>
@@ -23937,7 +23897,7 @@
       <c r="Q15" s="2"/>
       <c r="R15" s="2"/>
     </row>
-    <row r="16" spans="4:18" x14ac:dyDescent="0.3">
+    <row r="16" spans="4:18" x14ac:dyDescent="0.25">
       <c r="D16" s="77"/>
       <c r="E16" s="77"/>
       <c r="F16" s="77"/>
@@ -23952,86 +23912,86 @@
       <c r="Q16" s="2"/>
       <c r="R16" s="2"/>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="O17" s="2"/>
       <c r="P17" s="2"/>
       <c r="Q17" s="2"/>
       <c r="R17" s="2"/>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="O18" s="2"/>
       <c r="P18" s="2"/>
       <c r="Q18" s="2"/>
       <c r="R18" s="2"/>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B19" s="21"/>
       <c r="O19" s="2"/>
       <c r="P19" s="2"/>
       <c r="Q19" s="2"/>
       <c r="R19" s="2"/>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="O20" s="2"/>
       <c r="P20" s="2"/>
       <c r="Q20" s="2"/>
       <c r="R20" s="2"/>
     </row>
-    <row r="21" spans="1:18" ht="3.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O21" s="2"/>
       <c r="P21" s="2"/>
       <c r="Q21" s="2"/>
       <c r="R21" s="2"/>
     </row>
-    <row r="22" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="43" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B22" s="44"/>
       <c r="C22" t="s">
+        <v>1</v>
+      </c>
+      <c r="D22" t="s">
         <v>2</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>3</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>4</v>
       </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>5</v>
       </c>
-      <c r="G22" t="s">
+      <c r="H22" t="s">
         <v>6</v>
       </c>
-      <c r="H22" t="s">
+      <c r="I22" t="s">
         <v>7</v>
       </c>
-      <c r="I22" t="s">
+      <c r="J22" t="s">
         <v>8</v>
       </c>
-      <c r="J22" t="s">
+      <c r="K22" t="s">
         <v>9</v>
       </c>
-      <c r="K22" t="s">
+      <c r="L22" t="s">
         <v>10</v>
       </c>
-      <c r="L22" t="s">
+      <c r="M22" t="s">
         <v>11</v>
       </c>
-      <c r="M22" t="s">
+      <c r="N22" t="s">
         <v>12</v>
-      </c>
-      <c r="N22" t="s">
-        <v>13</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" s="2"/>
       <c r="Q22" s="2"/>
       <c r="R22" s="2"/>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="73" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B23" s="74"/>
       <c r="C23" s="22"/>
@@ -24051,12 +24011,12 @@
       <c r="Q23" s="2"/>
       <c r="R23" s="2"/>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="58" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C24" s="2">
         <f>'Prévisions Entrées-Encaiss'!C25</f>
@@ -24111,10 +24071,10 @@
       <c r="Q24" s="2"/>
       <c r="R24" s="2"/>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="59"/>
       <c r="B25" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C25" s="2">
         <f>'[1]Prévisions Entrées-Encaiss'!C26</f>
@@ -24169,10 +24129,10 @@
       <c r="Q25" s="2"/>
       <c r="R25" s="2"/>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="59"/>
       <c r="B26" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C26" s="2">
         <f>'[1]Prévisions Entrées-Encaiss'!C27</f>
@@ -24227,10 +24187,10 @@
       <c r="Q26" s="2"/>
       <c r="R26" s="2"/>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="59"/>
       <c r="B27" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C27" s="2">
         <f>'[1]Prévisions Entrées-Encaiss'!C28</f>
@@ -24285,10 +24245,10 @@
       <c r="Q27" s="2"/>
       <c r="R27" s="2"/>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="59"/>
       <c r="B28" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C28" s="2">
         <f>'[1]Prévisions Entrées-Encaiss'!C29</f>
@@ -24343,10 +24303,10 @@
       <c r="Q28" s="2"/>
       <c r="R28" s="2"/>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="59"/>
       <c r="B29" s="7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C29" s="2">
         <f>'[1]Prévisions Entrées-Encaiss'!C30</f>
@@ -24401,10 +24361,10 @@
       <c r="Q29" s="2"/>
       <c r="R29" s="2"/>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="59"/>
       <c r="B30" s="7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C30" s="2">
         <f>'[1]Prévisions Entrées-Encaiss'!C31</f>
@@ -24459,10 +24419,10 @@
       <c r="Q30" s="2"/>
       <c r="R30" s="2"/>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="59"/>
       <c r="B31" s="7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C31" s="2">
         <f>'[1]Prévisions Entrées-Encaiss'!C32</f>
@@ -24517,10 +24477,10 @@
       <c r="Q31" s="2"/>
       <c r="R31" s="2"/>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="59"/>
       <c r="B32" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C32" s="2">
         <f>'[1]Prévisions Entrées-Encaiss'!C33</f>
@@ -24575,10 +24535,10 @@
       <c r="Q32" s="2"/>
       <c r="R32" s="2"/>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" s="23"/>
       <c r="B33" s="7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C33" s="2">
         <f>'[1]Prévisions Entrées-Encaiss'!C34</f>
@@ -24633,9 +24593,9 @@
       <c r="Q33" s="2"/>
       <c r="R33" s="2"/>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" s="56" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B34" s="57"/>
       <c r="C34" s="2">
@@ -24691,9 +24651,9 @@
       <c r="Q34" s="2"/>
       <c r="R34" s="2"/>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" s="64" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B35" s="65"/>
       <c r="C35" s="9">
@@ -24749,9 +24709,9 @@
       <c r="Q35" s="2"/>
       <c r="R35" s="2"/>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" s="66" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B36" s="67"/>
       <c r="C36" s="24"/>
@@ -24771,9 +24731,9 @@
       <c r="Q36" s="2"/>
       <c r="R36" s="2"/>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" s="68" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B37" s="69"/>
       <c r="C37" s="15">
@@ -24829,9 +24789,9 @@
       <c r="Q37" s="2"/>
       <c r="R37" s="2"/>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" s="68" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B38" s="69"/>
       <c r="C38" s="15">
@@ -24887,9 +24847,9 @@
       <c r="Q38" s="2"/>
       <c r="R38" s="2"/>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" s="68" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B39" s="69"/>
       <c r="C39" s="15">
@@ -24945,9 +24905,9 @@
       <c r="Q39" s="2"/>
       <c r="R39" s="2"/>
     </row>
-    <row r="40" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="68" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B40" s="69"/>
       <c r="C40" s="15">
@@ -25003,9 +24963,9 @@
       <c r="Q40" s="2"/>
       <c r="R40" s="2"/>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" s="68" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B41" s="69"/>
       <c r="C41" s="15">
@@ -25061,12 +25021,12 @@
       <c r="Q41" s="2"/>
       <c r="R41" s="2"/>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" s="70" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B42" s="25" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C42" s="15">
         <f>'[1]Prévisions Dépenses-Décaiss'!C32</f>
@@ -25121,10 +25081,10 @@
       <c r="Q42" s="2"/>
       <c r="R42" s="2"/>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" s="71"/>
       <c r="B43" s="25" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C43" s="15">
         <f>'[1]Prévisions Dépenses-Décaiss'!C33</f>
@@ -25179,10 +25139,10 @@
       <c r="Q43" s="2"/>
       <c r="R43" s="2"/>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44" s="72"/>
       <c r="B44" s="25" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C44" s="15">
         <f>'[1]Prévisions Dépenses-Décaiss'!C34</f>
@@ -25237,9 +25197,9 @@
       <c r="Q44" s="2"/>
       <c r="R44" s="2"/>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45" s="68" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B45" s="69"/>
       <c r="C45" s="15">
@@ -25295,9 +25255,9 @@
       <c r="Q45" s="2"/>
       <c r="R45" s="2"/>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" s="68" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B46" s="69"/>
       <c r="C46" s="15">
@@ -25353,9 +25313,9 @@
       <c r="Q46" s="2"/>
       <c r="R46" s="2"/>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47" s="62" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B47" s="63"/>
       <c r="C47" s="9">
@@ -25411,9 +25371,9 @@
       <c r="Q47" s="2"/>
       <c r="R47" s="2"/>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48" s="50" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B48" s="50"/>
       <c r="C48" s="26"/>
@@ -25466,9 +25426,9 @@
       <c r="Q48" s="2"/>
       <c r="R48" s="2"/>
     </row>
-    <row r="49" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A49" s="60" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B49" s="61"/>
       <c r="C49" s="27">
@@ -25524,9 +25484,9 @@
       <c r="Q49" s="2"/>
       <c r="R49" s="2"/>
     </row>
-    <row r="50" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A50" s="50" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B50" s="50"/>
       <c r="C50" s="18">
@@ -25582,9 +25542,9 @@
       <c r="Q50" s="2"/>
       <c r="R50" s="2"/>
     </row>
-    <row r="51" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A51" s="50" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B51" s="50"/>
       <c r="C51" s="18">
@@ -25640,9 +25600,9 @@
       <c r="Q51" s="2"/>
       <c r="R51" s="2"/>
     </row>
-    <row r="52" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A52" s="50" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B52" s="50"/>
       <c r="C52" s="18">
@@ -25698,34 +25658,34 @@
       <c r="Q52" s="2"/>
       <c r="R52" s="2"/>
     </row>
-    <row r="53" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K53" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" s="2"/>
       <c r="Q53" s="2"/>
       <c r="R53" s="2"/>
       <c r="U53" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC53" t="s">
         <v>32</v>
       </c>
-      <c r="AC53" t="s">
-        <v>33</v>
-      </c>
     </row>
-    <row r="54" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:29" x14ac:dyDescent="0.25">
       <c r="D54" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" s="2"/>
       <c r="Q54" s="2"/>
       <c r="R54" s="2"/>
     </row>
-    <row r="55" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:29" x14ac:dyDescent="0.25">
       <c r="C55" s="2"/>
       <c r="M55" s="2"/>
       <c r="O55" s="2"/>
@@ -25733,61 +25693,61 @@
       <c r="Q55" s="2"/>
       <c r="R55" s="2"/>
     </row>
-    <row r="56" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:29" x14ac:dyDescent="0.25">
       <c r="O56" s="2"/>
       <c r="P56" s="2"/>
       <c r="Q56" s="2"/>
       <c r="R56" s="2"/>
     </row>
-    <row r="57" spans="1:29" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:29" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="43" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B57" s="44"/>
       <c r="C57" t="s">
+        <v>34</v>
+      </c>
+      <c r="D57" t="s">
         <v>35</v>
       </c>
-      <c r="D57" t="s">
+      <c r="E57" t="s">
         <v>36</v>
       </c>
-      <c r="E57" t="s">
+      <c r="F57" t="s">
         <v>37</v>
       </c>
-      <c r="F57" t="s">
+      <c r="G57" t="s">
         <v>38</v>
       </c>
-      <c r="G57" t="s">
+      <c r="H57" t="s">
         <v>39</v>
       </c>
-      <c r="H57" t="s">
+      <c r="I57" t="s">
         <v>40</v>
       </c>
-      <c r="I57" t="s">
+      <c r="J57" t="s">
         <v>41</v>
       </c>
-      <c r="J57" t="s">
+      <c r="K57" t="s">
         <v>42</v>
       </c>
-      <c r="K57" t="s">
+      <c r="L57" t="s">
         <v>43</v>
       </c>
-      <c r="L57" t="s">
+      <c r="M57" t="s">
         <v>44</v>
       </c>
-      <c r="M57" t="s">
+      <c r="N57" t="s">
         <v>45</v>
-      </c>
-      <c r="N57" t="s">
-        <v>46</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" s="2"/>
       <c r="Q57" s="2"/>
       <c r="R57" s="2"/>
     </row>
-    <row r="58" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A58" s="73" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B58" s="74"/>
       <c r="C58" s="22"/>
@@ -25807,12 +25767,12 @@
       <c r="Q58" s="2"/>
       <c r="R58" s="2"/>
     </row>
-    <row r="59" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A59" s="58" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C59" s="15">
         <f>'[1]Prévisions Entrées-Encaiss'!C42</f>
@@ -25867,13 +25827,13 @@
       <c r="Q59" s="2"/>
       <c r="R59" s="2"/>
       <c r="W59" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
-    <row r="60" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A60" s="59"/>
       <c r="B60" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C60" s="15">
         <f>'[1]Prévisions Entrées-Encaiss'!C43</f>
@@ -25928,13 +25888,13 @@
       <c r="Q60" s="2"/>
       <c r="R60" s="2"/>
       <c r="Y60" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
-    <row r="61" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A61" s="59"/>
       <c r="B61" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C61" s="15">
         <f>'[1]Prévisions Entrées-Encaiss'!C44</f>
@@ -25989,10 +25949,10 @@
       <c r="Q61" s="2"/>
       <c r="R61" s="2"/>
     </row>
-    <row r="62" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A62" s="59"/>
       <c r="B62" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C62" s="15">
         <f>'[1]Prévisions Entrées-Encaiss'!C45</f>
@@ -26047,13 +26007,13 @@
       <c r="Q62" s="2"/>
       <c r="R62" s="2"/>
       <c r="U62" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
-    <row r="63" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A63" s="59"/>
       <c r="B63" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C63" s="15">
         <f>'[1]Prévisions Entrées-Encaiss'!C46</f>
@@ -26108,10 +26068,10 @@
       <c r="Q63" s="2"/>
       <c r="R63" s="2"/>
     </row>
-    <row r="64" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A64" s="59"/>
       <c r="B64" s="7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C64" s="15">
         <f>'[1]Prévisions Entrées-Encaiss'!C47</f>
@@ -26166,10 +26126,10 @@
       <c r="Q64" s="2"/>
       <c r="R64" s="2"/>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A65" s="59"/>
       <c r="B65" s="7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C65" s="15">
         <f>'[1]Prévisions Entrées-Encaiss'!C48</f>
@@ -26224,10 +26184,10 @@
       <c r="Q65" s="2"/>
       <c r="R65" s="2"/>
     </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A66" s="59"/>
       <c r="B66" s="7" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C66" s="15">
         <f>'[1]Prévisions Entrées-Encaiss'!C49</f>
@@ -26282,10 +26242,10 @@
       <c r="Q66" s="2"/>
       <c r="R66" s="2"/>
     </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67" s="59"/>
       <c r="B67" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C67" s="15">
         <f>'[1]Prévisions Entrées-Encaiss'!C50</f>
@@ -26340,10 +26300,10 @@
       <c r="Q67" s="2"/>
       <c r="R67" s="2"/>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68" s="59"/>
       <c r="B68" s="7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C68" s="15">
         <f>'[1]Prévisions Entrées-Encaiss'!C51</f>
@@ -26398,9 +26358,9 @@
       <c r="Q68" s="2"/>
       <c r="R68" s="2"/>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A69" s="56" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B69" s="57"/>
       <c r="C69" s="15">
@@ -26456,9 +26416,9 @@
       <c r="Q69" s="2"/>
       <c r="R69" s="2"/>
     </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70" s="64" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B70" s="65"/>
       <c r="C70" s="29">
@@ -26514,9 +26474,9 @@
       <c r="Q70" s="2"/>
       <c r="R70" s="2"/>
     </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A71" s="66" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B71" s="67"/>
       <c r="C71" s="30"/>
@@ -26536,9 +26496,9 @@
       <c r="Q71" s="2"/>
       <c r="R71" s="2"/>
     </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A72" s="68" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B72" s="69"/>
       <c r="C72" s="15">
@@ -26594,9 +26554,9 @@
       <c r="Q72" s="2"/>
       <c r="R72" s="2"/>
     </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73" s="68" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B73" s="69"/>
       <c r="C73" s="15">
@@ -26652,9 +26612,9 @@
       <c r="Q73" s="2"/>
       <c r="R73" s="2"/>
     </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74" s="68" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B74" s="69"/>
       <c r="C74" s="15">
@@ -26710,9 +26670,9 @@
       <c r="Q74" s="2"/>
       <c r="R74" s="2"/>
     </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75" s="68" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B75" s="69"/>
       <c r="C75" s="15">
@@ -26768,9 +26728,9 @@
       <c r="Q75" s="2"/>
       <c r="R75" s="2"/>
     </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76" s="68" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B76" s="69"/>
       <c r="C76" s="15">
@@ -26826,12 +26786,12 @@
       <c r="Q76" s="2"/>
       <c r="R76" s="2"/>
     </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77" s="70" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B77" s="31" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C77" s="15">
         <f>'[1]Prévisions Dépenses-Décaiss'!C50</f>
@@ -26886,10 +26846,10 @@
       <c r="Q77" s="2"/>
       <c r="R77" s="2"/>
     </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78" s="71"/>
       <c r="B78" s="31" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C78" s="15">
         <f>'[1]Prévisions Dépenses-Décaiss'!C51</f>
@@ -26944,10 +26904,10 @@
       <c r="Q78" s="2"/>
       <c r="R78" s="2"/>
     </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" s="72"/>
       <c r="B79" s="32" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C79" s="15">
         <f>'[1]Prévisions Dépenses-Décaiss'!C52</f>
@@ -27002,9 +26962,9 @@
       <c r="Q79" s="2"/>
       <c r="R79" s="2"/>
     </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80" s="68" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B80" s="69"/>
       <c r="C80" s="15">
@@ -27060,9 +27020,9 @@
       <c r="Q80" s="2"/>
       <c r="R80" s="2"/>
     </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" s="68" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B81" s="69"/>
       <c r="C81" s="15">
@@ -27118,9 +27078,9 @@
       <c r="Q81" s="2"/>
       <c r="R81" s="2"/>
     </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82" s="62" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B82" s="63"/>
       <c r="C82" s="29">
@@ -27176,9 +27136,9 @@
       <c r="Q82" s="2"/>
       <c r="R82" s="2"/>
     </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" s="60" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B83" s="61"/>
       <c r="C83" s="33">
@@ -27234,9 +27194,9 @@
       <c r="Q83" s="2"/>
       <c r="R83" s="2"/>
     </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" s="60" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B84" s="61"/>
       <c r="C84" s="35">
@@ -27292,9 +27252,9 @@
       <c r="Q84" s="2"/>
       <c r="R84" s="2"/>
     </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" s="60" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B85" s="61"/>
       <c r="C85" s="35">
@@ -27350,9 +27310,9 @@
       <c r="Q85" s="2"/>
       <c r="R85" s="2"/>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" s="60" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B86" s="61"/>
       <c r="C86" s="35">
@@ -27408,9 +27368,9 @@
       <c r="Q86" s="2"/>
       <c r="R86" s="2"/>
     </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" s="50" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B87" s="50"/>
       <c r="C87" s="35">
@@ -27466,30 +27426,30 @@
       <c r="Q87" s="2"/>
       <c r="R87" s="2"/>
     </row>
-    <row r="88" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="K88" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" s="2"/>
       <c r="Q88" s="2"/>
       <c r="R88" s="2"/>
     </row>
-    <row r="89" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E89" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K89" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q89" s="2"/>
       <c r="R89" s="2"/>
     </row>
-    <row r="90" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C90" s="76"/>
       <c r="D90" s="76"/>
       <c r="J90" s="75"/>
@@ -27499,61 +27459,61 @@
       <c r="Q90" s="2"/>
       <c r="R90" s="2"/>
     </row>
-    <row r="91" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O91" s="2"/>
       <c r="P91" s="2"/>
       <c r="Q91" s="2"/>
       <c r="R91" s="2"/>
     </row>
-    <row r="92" spans="1:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="43" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B92" s="44"/>
       <c r="C92" t="s">
+        <v>47</v>
+      </c>
+      <c r="D92" t="s">
         <v>48</v>
       </c>
-      <c r="D92" t="s">
+      <c r="E92" t="s">
         <v>49</v>
       </c>
-      <c r="E92" t="s">
+      <c r="F92" t="s">
         <v>50</v>
       </c>
-      <c r="F92" t="s">
+      <c r="G92" t="s">
         <v>51</v>
       </c>
-      <c r="G92" t="s">
+      <c r="H92" t="s">
         <v>52</v>
       </c>
-      <c r="H92" t="s">
+      <c r="I92" t="s">
         <v>53</v>
       </c>
-      <c r="I92" t="s">
+      <c r="J92" t="s">
         <v>54</v>
       </c>
-      <c r="J92" t="s">
+      <c r="K92" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="K92" s="2" t="s">
+      <c r="L92" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="L92" s="2" t="s">
+      <c r="M92" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="M92" s="2" t="s">
-        <v>58</v>
-      </c>
       <c r="N92" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" s="2"/>
       <c r="Q92" s="2"/>
       <c r="R92" s="2"/>
     </row>
-    <row r="93" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="73" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B93" s="74"/>
       <c r="C93" s="22"/>
@@ -27573,12 +27533,12 @@
       <c r="Q93" s="2"/>
       <c r="R93" s="2"/>
     </row>
-    <row r="94" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="58" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C94" s="2">
         <f>'[1]Prévisions Entrées-Encaiss'!C59</f>
@@ -27633,10 +27593,10 @@
       <c r="Q94" s="2"/>
       <c r="R94" s="2"/>
     </row>
-    <row r="95" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="59"/>
       <c r="B95" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C95" s="2">
         <f>'[1]Prévisions Entrées-Encaiss'!C60</f>
@@ -27691,10 +27651,10 @@
       <c r="Q95" s="2"/>
       <c r="R95" s="2"/>
     </row>
-    <row r="96" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="59"/>
       <c r="B96" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C96" s="2">
         <f>'[1]Prévisions Entrées-Encaiss'!C61</f>
@@ -27749,10 +27709,10 @@
       <c r="Q96" s="2"/>
       <c r="R96" s="2"/>
     </row>
-    <row r="97" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="59"/>
       <c r="B97" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C97" s="2">
         <f>'[1]Prévisions Entrées-Encaiss'!C62</f>
@@ -27807,10 +27767,10 @@
       <c r="Q97" s="2"/>
       <c r="R97" s="2"/>
     </row>
-    <row r="98" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="59"/>
       <c r="B98" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C98" s="2">
         <f>'[1]Prévisions Entrées-Encaiss'!C63</f>
@@ -27865,10 +27825,10 @@
       <c r="Q98" s="2"/>
       <c r="R98" s="2"/>
     </row>
-    <row r="99" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="59"/>
       <c r="B99" s="7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C99" s="2">
         <f>'[1]Prévisions Entrées-Encaiss'!C64</f>
@@ -27923,10 +27883,10 @@
       <c r="Q99" s="2"/>
       <c r="R99" s="2"/>
     </row>
-    <row r="100" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="59"/>
       <c r="B100" s="7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C100" s="2">
         <f>'[1]Prévisions Entrées-Encaiss'!C65</f>
@@ -27981,10 +27941,10 @@
       <c r="Q100" s="2"/>
       <c r="R100" s="2"/>
     </row>
-    <row r="101" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="59"/>
       <c r="B101" s="7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C101" s="2">
         <f>'[1]Prévisions Entrées-Encaiss'!C66</f>
@@ -28039,10 +27999,10 @@
       <c r="Q101" s="2"/>
       <c r="R101" s="2"/>
     </row>
-    <row r="102" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="59"/>
       <c r="B102" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C102" s="2">
         <f>'[1]Prévisions Entrées-Encaiss'!C67</f>
@@ -28097,10 +28057,10 @@
       <c r="Q102" s="2"/>
       <c r="R102" s="2"/>
     </row>
-    <row r="103" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="59"/>
       <c r="B103" s="7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C103" s="2">
         <f>'[1]Prévisions Entrées-Encaiss'!C68</f>
@@ -28155,9 +28115,9 @@
       <c r="Q103" s="2"/>
       <c r="R103" s="2"/>
     </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A104" s="56" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B104" s="57"/>
       <c r="C104" s="2">
@@ -28213,9 +28173,9 @@
       <c r="Q104" s="2"/>
       <c r="R104" s="2"/>
     </row>
-    <row r="105" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A105" s="64" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B105" s="65"/>
       <c r="C105" s="9">
@@ -28271,9 +28231,9 @@
       <c r="Q105" s="2"/>
       <c r="R105" s="2"/>
     </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A106" s="66" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B106" s="67"/>
       <c r="C106" s="24"/>
@@ -28293,9 +28253,9 @@
       <c r="Q106" s="2"/>
       <c r="R106" s="2"/>
     </row>
-    <row r="107" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A107" s="68" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B107" s="69"/>
       <c r="C107" s="2">
@@ -28351,9 +28311,9 @@
       <c r="Q107" s="2"/>
       <c r="R107" s="2"/>
     </row>
-    <row r="108" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A108" s="68" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B108" s="69"/>
       <c r="C108" s="2">
@@ -28409,9 +28369,9 @@
       <c r="Q108" s="2"/>
       <c r="R108" s="2"/>
     </row>
-    <row r="109" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A109" s="68" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B109" s="69"/>
       <c r="C109" s="2">
@@ -28467,9 +28427,9 @@
       <c r="Q109" s="2"/>
       <c r="R109" s="2"/>
     </row>
-    <row r="110" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A110" s="68" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B110" s="69"/>
       <c r="C110" s="2">
@@ -28525,9 +28485,9 @@
       <c r="Q110" s="2"/>
       <c r="R110" s="2"/>
     </row>
-    <row r="111" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A111" s="68" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B111" s="69"/>
       <c r="C111" s="2">
@@ -28583,12 +28543,12 @@
       <c r="Q111" s="2"/>
       <c r="R111" s="2"/>
     </row>
-    <row r="112" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A112" s="70" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B112" s="31" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C112" s="2">
         <f>'[1]Prévisions Dépenses-Décaiss'!C68</f>
@@ -28643,10 +28603,10 @@
       <c r="Q112" s="2"/>
       <c r="R112" s="2"/>
     </row>
-    <row r="113" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A113" s="71"/>
       <c r="B113" s="31" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C113" s="2">
         <f>'[1]Prévisions Dépenses-Décaiss'!C69</f>
@@ -28701,10 +28661,10 @@
       <c r="Q113" s="2"/>
       <c r="R113" s="2"/>
     </row>
-    <row r="114" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A114" s="72"/>
       <c r="B114" s="32" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C114" s="2">
         <f>'[1]Prévisions Dépenses-Décaiss'!C70</f>
@@ -28759,9 +28719,9 @@
       <c r="Q114" s="2"/>
       <c r="R114" s="2"/>
     </row>
-    <row r="115" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A115" s="68" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B115" s="69"/>
       <c r="C115" s="2">
@@ -28817,9 +28777,9 @@
       <c r="Q115" s="2"/>
       <c r="R115" s="2"/>
     </row>
-    <row r="116" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A116" s="68" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B116" s="69"/>
       <c r="C116" s="2">
@@ -28876,9 +28836,9 @@
       <c r="R116" s="2"/>
       <c r="S116" s="2"/>
     </row>
-    <row r="117" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A117" s="62" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B117" s="63"/>
       <c r="C117" s="9">
@@ -28934,9 +28894,9 @@
       <c r="Q117" s="2"/>
       <c r="R117" s="2"/>
     </row>
-    <row r="118" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A118" s="60" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B118" s="61"/>
       <c r="C118" s="26">
@@ -28992,9 +28952,9 @@
       <c r="Q118" s="2"/>
       <c r="R118" s="2"/>
     </row>
-    <row r="119" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A119" s="60" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B119" s="61"/>
       <c r="C119" s="18">
@@ -29050,9 +29010,9 @@
       <c r="Q119" s="2"/>
       <c r="R119" s="2"/>
     </row>
-    <row r="120" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A120" s="60" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B120" s="61"/>
       <c r="C120" s="18">
@@ -29108,9 +29068,9 @@
       <c r="Q120" s="2"/>
       <c r="R120" s="2"/>
     </row>
-    <row r="121" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A121" s="60" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B121" s="61"/>
       <c r="C121" s="18">
@@ -29166,9 +29126,9 @@
       <c r="Q121" s="2"/>
       <c r="R121" s="2"/>
     </row>
-    <row r="122" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A122" s="60" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B122" s="61"/>
       <c r="C122" s="18">
@@ -29224,7 +29184,7 @@
       <c r="Q122" s="2"/>
       <c r="R122" s="2"/>
     </row>
-    <row r="123" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:19" x14ac:dyDescent="0.25">
       <c r="C123" s="2"/>
       <c r="L123" s="2"/>
       <c r="M123" s="2"/>
@@ -29234,7 +29194,7 @@
       <c r="Q123" s="2"/>
       <c r="R123" s="2"/>
     </row>
-    <row r="124" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:19" x14ac:dyDescent="0.25">
       <c r="L124" s="2"/>
       <c r="M124" s="2"/>
       <c r="N124" s="2"/>
@@ -29243,66 +29203,66 @@
       <c r="Q124" s="2"/>
       <c r="R124" s="2"/>
     </row>
-    <row r="125" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A125" s="43" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B125" s="44"/>
       <c r="C125" t="s">
+        <v>59</v>
+      </c>
+      <c r="D125" t="s">
         <v>60</v>
       </c>
-      <c r="D125" t="s">
+      <c r="E125" t="s">
         <v>61</v>
       </c>
-      <c r="E125" t="s">
-        <v>62</v>
-      </c>
       <c r="F125" t="s">
+        <v>99</v>
+      </c>
+      <c r="G125" t="s">
+        <v>63</v>
+      </c>
+      <c r="H125" t="s">
+        <v>64</v>
+      </c>
+      <c r="I125" t="s">
+        <v>65</v>
+      </c>
+      <c r="J125" t="s">
+        <v>100</v>
+      </c>
+      <c r="K125" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="L125" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="M125" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="N125" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="G125" t="s">
-        <v>64</v>
-      </c>
-      <c r="H125" t="s">
-        <v>65</v>
-      </c>
-      <c r="I125" t="s">
-        <v>66</v>
-      </c>
-      <c r="J125" t="s">
-        <v>102</v>
-      </c>
-      <c r="K125" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="L125" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="M125" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="N125" s="2" t="s">
-        <v>103</v>
-      </c>
       <c r="O125" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P125" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="P125" s="2" t="s">
+      <c r="Q125" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q125" s="2" t="s">
+      <c r="R125" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="R125" s="2" t="s">
-        <v>5</v>
-      </c>
       <c r="S125" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
-    <row r="126" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A126" s="73" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B126" s="74"/>
       <c r="C126" s="22"/>
@@ -29323,12 +29283,12 @@
       <c r="R126" s="22"/>
       <c r="S126" s="22"/>
     </row>
-    <row r="127" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A127" s="58" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C127" s="2">
         <f>'[1]Prévisions Entrées-Encaiss'!C76</f>
@@ -29399,10 +29359,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A128" s="59"/>
       <c r="B128" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C128" s="2">
         <f>'[1]Prévisions Entrées-Encaiss'!C77</f>
@@ -29473,10 +29433,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A129" s="59"/>
       <c r="B129" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C129" s="2">
         <f>'[1]Prévisions Entrées-Encaiss'!C78</f>
@@ -29547,10 +29507,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A130" s="59"/>
       <c r="B130" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C130" s="2">
         <f>'[1]Prévisions Entrées-Encaiss'!C79</f>
@@ -29621,10 +29581,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A131" s="59"/>
       <c r="B131" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C131" s="2">
         <f>'[1]Prévisions Entrées-Encaiss'!C80</f>
@@ -29695,10 +29655,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A132" s="59"/>
       <c r="B132" s="7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C132" s="2">
         <f>'[1]Prévisions Entrées-Encaiss'!C81</f>
@@ -29769,10 +29729,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A133" s="59"/>
       <c r="B133" s="7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C133" s="2">
         <f>'[1]Prévisions Entrées-Encaiss'!C82</f>
@@ -29843,10 +29803,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A134" s="59"/>
       <c r="B134" s="7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C134" s="2">
         <f>'[1]Prévisions Entrées-Encaiss'!C83</f>
@@ -29917,10 +29877,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A135" s="59"/>
       <c r="B135" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C135" s="2">
         <f>'[1]Prévisions Entrées-Encaiss'!C84</f>
@@ -29991,10 +29951,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A136" s="59"/>
       <c r="B136" s="7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C136" s="2">
         <f>'[1]Prévisions Entrées-Encaiss'!C85</f>
@@ -30065,9 +30025,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A137" s="56" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B137" s="57"/>
       <c r="C137" s="2">
@@ -30139,9 +30099,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A138" s="64" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B138" s="65"/>
       <c r="C138" s="9">
@@ -30213,9 +30173,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A139" s="66" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B139" s="67"/>
       <c r="C139" s="24"/>
@@ -30236,9 +30196,9 @@
       <c r="R139" s="24"/>
       <c r="S139" s="24"/>
     </row>
-    <row r="140" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A140" s="68" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B140" s="69"/>
       <c r="C140" s="2">
@@ -30310,9 +30270,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A141" s="68" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B141" s="69"/>
       <c r="C141" s="2">
@@ -30384,9 +30344,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A142" s="68" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B142" s="69"/>
       <c r="C142" s="2">
@@ -30458,9 +30418,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A143" s="68" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B143" s="69"/>
       <c r="C143" s="2">
@@ -30532,9 +30492,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A144" s="68" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B144" s="69"/>
       <c r="C144" s="2">
@@ -30606,12 +30566,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A145" s="70" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B145" s="31" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C145" s="2">
         <f>'[1]Prévisions Dépenses-Décaiss'!C86</f>
@@ -30682,10 +30642,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A146" s="71"/>
       <c r="B146" s="31" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C146" s="2">
         <f>'[1]Prévisions Dépenses-Décaiss'!C87</f>
@@ -30756,10 +30716,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A147" s="72"/>
       <c r="B147" s="32" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C147" s="2">
         <f>'[1]Prévisions Dépenses-Décaiss'!C88</f>
@@ -30830,9 +30790,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A148" s="68" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B148" s="69"/>
       <c r="C148" s="2">
@@ -30904,9 +30864,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A149" s="68" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B149" s="69"/>
       <c r="C149" s="2">
@@ -30978,9 +30938,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A150" s="62" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B150" s="63"/>
       <c r="C150" s="9">
@@ -31052,9 +31012,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A151" s="60" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B151" s="61"/>
       <c r="C151" s="26">
@@ -31126,9 +31086,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A152" s="60" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B152" s="61"/>
       <c r="C152" s="18">
@@ -31200,9 +31160,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A153" s="60" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B153" s="61"/>
       <c r="C153" s="18">
@@ -31274,9 +31234,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A154" s="60" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B154" s="61"/>
       <c r="C154" s="18">
@@ -31348,9 +31308,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A155" s="60" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B155" s="61"/>
       <c r="C155" s="18">
@@ -31422,24 +31382,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:19" x14ac:dyDescent="0.25">
       <c r="C156" s="2"/>
     </row>
-    <row r="157" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:19" x14ac:dyDescent="0.25">
       <c r="C157" s="39"/>
       <c r="D157" s="2"/>
     </row>
-    <row r="159" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:19" x14ac:dyDescent="0.25">
       <c r="H159" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
-    <row r="160" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:19" x14ac:dyDescent="0.25">
       <c r="I160" s="40"/>
     </row>
-    <row r="162" spans="13:13" x14ac:dyDescent="0.3">
+    <row r="162" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M162" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -31528,92 +31488,94 @@
     <mergeCell ref="A154:B154"/>
     <mergeCell ref="A155:B155"/>
   </mergeCells>
+  <conditionalFormatting sqref="C83">
+    <cfRule type="cellIs" dxfId="40" priority="35" operator="lessThan">
+      <formula>$C$82</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C118">
+    <cfRule type="cellIs" dxfId="39" priority="18" operator="lessThan">
+      <formula>$C$82</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C151">
+    <cfRule type="cellIs" dxfId="38" priority="6" operator="lessThan">
+      <formula>$C$82</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D48">
+    <cfRule type="cellIs" dxfId="37" priority="26" operator="lessThan">
+      <formula>$D$47</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D83">
+    <cfRule type="cellIs" dxfId="36" priority="21" operator="lessThan">
+      <formula>$D$82</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D118">
+    <cfRule type="cellIs" dxfId="35" priority="9" operator="lessThan">
+      <formula>$D$82</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D151">
+    <cfRule type="cellIs" dxfId="34" priority="1" operator="lessThan">
+      <formula>$D$82</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E83">
+    <cfRule type="cellIs" dxfId="33" priority="34" operator="lessThan">
+      <formula>$E$82</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E118">
+    <cfRule type="cellIs" dxfId="32" priority="17" operator="lessThan">
+      <formula>$E$82</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E151">
+    <cfRule type="cellIs" dxfId="31" priority="5" operator="lessThan">
+      <formula>$E$82</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F48">
+    <cfRule type="cellIs" dxfId="30" priority="25" operator="lessThan">
+      <formula>$F$47</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F83">
+    <cfRule type="cellIs" dxfId="29" priority="33" operator="lessThan">
+      <formula>$F$82</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F118">
+    <cfRule type="cellIs" dxfId="28" priority="16" operator="lessThan">
+      <formula>$F$82</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F151">
+    <cfRule type="cellIs" dxfId="27" priority="4" operator="lessThan">
+      <formula>$F$82</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="G48">
-    <cfRule type="cellIs" dxfId="40" priority="41" operator="lessThan">
+    <cfRule type="cellIs" dxfId="26" priority="41" operator="lessThan">
       <formula>$G$37</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I48">
-    <cfRule type="cellIs" dxfId="39" priority="40" operator="lessThan">
-      <formula>$I$47</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J48">
-    <cfRule type="cellIs" dxfId="38" priority="39" operator="lessThan">
-      <formula>$J$47</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K48">
-    <cfRule type="cellIs" dxfId="37" priority="38" operator="lessThan">
-      <formula>$K$47</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M48">
-    <cfRule type="cellIs" dxfId="36" priority="22" operator="lessThan">
-      <formula>$M$47</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="35" priority="37" operator="lessThan">
-      <formula>$M$47</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N48">
-    <cfRule type="cellIs" dxfId="34" priority="36" operator="lessThan">
-      <formula>$N$47</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C83">
-    <cfRule type="cellIs" dxfId="33" priority="35" operator="lessThan">
-      <formula>$C$82</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E83">
-    <cfRule type="cellIs" dxfId="32" priority="34" operator="lessThan">
-      <formula>$E$82</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F83">
-    <cfRule type="cellIs" dxfId="31" priority="33" operator="lessThan">
-      <formula>$F$82</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="G83">
-    <cfRule type="cellIs" dxfId="30" priority="32" operator="lessThan">
+    <cfRule type="cellIs" dxfId="25" priority="32" operator="lessThan">
       <formula>$G$82</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I83">
-    <cfRule type="cellIs" dxfId="29" priority="31" operator="lessThan">
-      <formula>$I$82</formula>
+  <conditionalFormatting sqref="G118">
+    <cfRule type="cellIs" dxfId="24" priority="15" operator="lessThan">
+      <formula>$G$82</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J83">
-    <cfRule type="cellIs" dxfId="28" priority="30" operator="lessThan">
-      <formula>$J$82</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K83">
-    <cfRule type="cellIs" dxfId="27" priority="29" operator="lessThan">
-      <formula>$K$82</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M83">
-    <cfRule type="cellIs" dxfId="26" priority="28" operator="lessThan">
-      <formula>$M$82</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N83">
-    <cfRule type="cellIs" dxfId="25" priority="27" operator="lessThan">
-      <formula>$N$82</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D48">
-    <cfRule type="cellIs" dxfId="24" priority="26" operator="lessThan">
-      <formula>$D$47</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F48">
-    <cfRule type="cellIs" dxfId="23" priority="25" operator="lessThan">
-      <formula>$F$47</formula>
+  <conditionalFormatting sqref="G151:R151">
+    <cfRule type="cellIs" dxfId="23" priority="3" operator="lessThan">
+      <formula>$G$82</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H48">
@@ -31621,54 +31583,54 @@
       <formula>$H$47</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L48">
-    <cfRule type="cellIs" dxfId="21" priority="23" operator="lessThan">
-      <formula>$L$47</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D83">
-    <cfRule type="cellIs" dxfId="20" priority="21" operator="lessThan">
-      <formula>$D$82</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="H83">
-    <cfRule type="cellIs" dxfId="19" priority="20" operator="lessThan">
+    <cfRule type="cellIs" dxfId="21" priority="20" operator="lessThan">
       <formula>$H$82</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L83">
-    <cfRule type="cellIs" dxfId="18" priority="19" operator="lessThan">
-      <formula>$L$82</formula>
+  <conditionalFormatting sqref="H118">
+    <cfRule type="cellIs" dxfId="20" priority="8" operator="lessThan">
+      <formula>$H$82</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C118">
-    <cfRule type="cellIs" dxfId="17" priority="18" operator="lessThan">
-      <formula>$C$82</formula>
+  <conditionalFormatting sqref="I48">
+    <cfRule type="cellIs" dxfId="19" priority="40" operator="lessThan">
+      <formula>$I$47</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E118">
-    <cfRule type="cellIs" dxfId="16" priority="17" operator="lessThan">
-      <formula>$E$82</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F118">
-    <cfRule type="cellIs" dxfId="15" priority="16" operator="lessThan">
-      <formula>$F$82</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G118">
-    <cfRule type="cellIs" dxfId="14" priority="15" operator="lessThan">
-      <formula>$G$82</formula>
+  <conditionalFormatting sqref="I83">
+    <cfRule type="cellIs" dxfId="18" priority="31" operator="lessThan">
+      <formula>$I$82</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I118">
-    <cfRule type="cellIs" dxfId="13" priority="14" operator="lessThan">
+    <cfRule type="cellIs" dxfId="17" priority="14" operator="lessThan">
       <formula>$I$82</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="J48">
+    <cfRule type="cellIs" dxfId="16" priority="39" operator="lessThan">
+      <formula>$J$47</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J83">
+    <cfRule type="cellIs" dxfId="15" priority="30" operator="lessThan">
+      <formula>$J$82</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="J118">
-    <cfRule type="cellIs" dxfId="12" priority="13" operator="lessThan">
+    <cfRule type="cellIs" dxfId="14" priority="13" operator="lessThan">
       <formula>$J$82</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K48">
+    <cfRule type="cellIs" dxfId="13" priority="38" operator="lessThan">
+      <formula>$K$47</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K83">
+    <cfRule type="cellIs" dxfId="12" priority="29" operator="lessThan">
+      <formula>$K$82</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K118">
@@ -31676,59 +31638,57 @@
       <formula>$K$82</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M118">
-    <cfRule type="cellIs" dxfId="10" priority="11" operator="lessThan">
+  <conditionalFormatting sqref="L48">
+    <cfRule type="cellIs" dxfId="10" priority="23" operator="lessThan">
+      <formula>$L$47</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L83">
+    <cfRule type="cellIs" dxfId="9" priority="19" operator="lessThan">
+      <formula>$L$82</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L118">
+    <cfRule type="cellIs" dxfId="8" priority="7" operator="lessThan">
+      <formula>$L$82</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M48">
+    <cfRule type="cellIs" dxfId="7" priority="22" operator="lessThan">
+      <formula>$M$47</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="37" operator="lessThan">
+      <formula>$M$47</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M83">
+    <cfRule type="cellIs" dxfId="5" priority="28" operator="lessThan">
       <formula>$M$82</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N118">
-    <cfRule type="cellIs" dxfId="9" priority="10" operator="lessThan">
+  <conditionalFormatting sqref="M118">
+    <cfRule type="cellIs" dxfId="4" priority="11" operator="lessThan">
+      <formula>$M$82</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N48">
+    <cfRule type="cellIs" dxfId="3" priority="36" operator="lessThan">
+      <formula>$N$47</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N83">
+    <cfRule type="cellIs" dxfId="2" priority="27" operator="lessThan">
       <formula>$N$82</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D118">
-    <cfRule type="cellIs" dxfId="8" priority="9" operator="lessThan">
-      <formula>$D$82</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H118">
-    <cfRule type="cellIs" dxfId="7" priority="8" operator="lessThan">
-      <formula>$H$82</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L118">
-    <cfRule type="cellIs" dxfId="6" priority="7" operator="lessThan">
-      <formula>$L$82</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C151">
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="lessThan">
-      <formula>$C$82</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E151">
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="lessThan">
-      <formula>$E$82</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F151">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="lessThan">
-      <formula>$F$82</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G151:R151">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="lessThan">
-      <formula>$G$82</formula>
+  <conditionalFormatting sqref="N118">
+    <cfRule type="cellIs" dxfId="1" priority="10" operator="lessThan">
+      <formula>$N$82</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S151">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>$N$82</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D151">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
-      <formula>$D$82</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
